--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703142</v>
+        <v>125703128</v>
       </c>
       <c r="B2" t="n">
         <v>78967</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502396</v>
+        <v>502289</v>
       </c>
       <c r="R2" t="n">
-        <v>6761943</v>
+        <v>6762035</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703036</v>
+        <v>125703034</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502277</v>
+        <v>502119</v>
       </c>
       <c r="R3" t="n">
-        <v>6762122</v>
+        <v>6762355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703141</v>
+        <v>125703142</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502408</v>
+        <v>502396</v>
       </c>
       <c r="R4" t="n">
-        <v>6761981</v>
+        <v>6761943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703117</v>
+        <v>125703036</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502502</v>
+        <v>502277</v>
       </c>
       <c r="R5" t="n">
-        <v>6761684</v>
+        <v>6762122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703128</v>
+        <v>125703141</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502289</v>
+        <v>502408</v>
       </c>
       <c r="R6" t="n">
-        <v>6762035</v>
+        <v>6761981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703034</v>
+        <v>125703117</v>
       </c>
       <c r="B7" t="n">
         <v>78967</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502119</v>
+        <v>502502</v>
       </c>
       <c r="R7" t="n">
-        <v>6762355</v>
+        <v>6761684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703111</v>
+        <v>125703156</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502516</v>
+        <v>502540</v>
       </c>
       <c r="R22" t="n">
-        <v>6761612</v>
+        <v>6761708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703125</v>
+        <v>125703119</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502314</v>
+        <v>502363</v>
       </c>
       <c r="R23" t="n">
-        <v>6762028</v>
+        <v>6761945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703032</v>
+        <v>125703111</v>
       </c>
       <c r="B24" t="n">
-        <v>97208</v>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502146</v>
+        <v>502516</v>
       </c>
       <c r="R24" t="n">
-        <v>6762231</v>
+        <v>6761612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703156</v>
+        <v>125703032</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>97208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502540</v>
+        <v>502146</v>
       </c>
       <c r="R25" t="n">
-        <v>6761708</v>
+        <v>6762231</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703119</v>
+        <v>125703125</v>
       </c>
       <c r="B26" t="n">
         <v>78967</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502363</v>
+        <v>502314</v>
       </c>
       <c r="R26" t="n">
-        <v>6761945</v>
+        <v>6762028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6495,7 +6495,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125703135</v>
+        <v>125703041</v>
       </c>
       <c r="B62" t="n">
         <v>78967</v>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502441</v>
+        <v>502202</v>
       </c>
       <c r="R62" t="n">
-        <v>6761973</v>
+        <v>6762136</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6592,7 +6592,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125703045</v>
+        <v>125703135</v>
       </c>
       <c r="B63" t="n">
         <v>78967</v>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502143</v>
+        <v>502441</v>
       </c>
       <c r="R63" t="n">
-        <v>6762252</v>
+        <v>6761973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6689,7 +6689,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125703041</v>
+        <v>125703045</v>
       </c>
       <c r="B64" t="n">
         <v>78967</v>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502202</v>
+        <v>502143</v>
       </c>
       <c r="R64" t="n">
-        <v>6762136</v>
+        <v>6762252</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125704222</v>
+        <v>125704055</v>
       </c>
       <c r="B94" t="n">
         <v>78967</v>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD94" t="b">

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703034</v>
+        <v>125703141</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502119</v>
+        <v>502408</v>
       </c>
       <c r="R3" t="n">
-        <v>6762355</v>
+        <v>6761981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703142</v>
+        <v>125703034</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502396</v>
+        <v>502119</v>
       </c>
       <c r="R4" t="n">
-        <v>6761943</v>
+        <v>6762355</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703036</v>
+        <v>125703117</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502277</v>
+        <v>502502</v>
       </c>
       <c r="R5" t="n">
-        <v>6762122</v>
+        <v>6761684</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703141</v>
+        <v>125703142</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502408</v>
+        <v>502396</v>
       </c>
       <c r="R6" t="n">
-        <v>6761981</v>
+        <v>6761943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703117</v>
+        <v>125703036</v>
       </c>
       <c r="B7" t="n">
         <v>78967</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502502</v>
+        <v>502277</v>
       </c>
       <c r="R7" t="n">
-        <v>6761684</v>
+        <v>6762122</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703116</v>
+        <v>125703121</v>
       </c>
       <c r="B9" t="n">
         <v>78967</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502499</v>
+        <v>502337</v>
       </c>
       <c r="R9" t="n">
-        <v>6761670</v>
+        <v>6761987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703109</v>
+        <v>125703116</v>
       </c>
       <c r="B10" t="n">
         <v>78967</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502522</v>
+        <v>502499</v>
       </c>
       <c r="R10" t="n">
-        <v>6761590</v>
+        <v>6761670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703134</v>
+        <v>125703109</v>
       </c>
       <c r="B11" t="n">
         <v>78967</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502457</v>
+        <v>502522</v>
       </c>
       <c r="R11" t="n">
-        <v>6761959</v>
+        <v>6761590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703121</v>
+        <v>125703134</v>
       </c>
       <c r="B12" t="n">
         <v>78967</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502337</v>
+        <v>502457</v>
       </c>
       <c r="R12" t="n">
-        <v>6761987</v>
+        <v>6761959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703140</v>
+        <v>125703158</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502377</v>
+        <v>502561</v>
       </c>
       <c r="R15" t="n">
-        <v>6761992</v>
+        <v>6761653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R18" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703049</v>
+        <v>125703148</v>
       </c>
       <c r="B20" t="n">
         <v>78967</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502125</v>
+        <v>502479</v>
       </c>
       <c r="R20" t="n">
-        <v>6762284</v>
+        <v>6761918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125703148</v>
+        <v>125703049</v>
       </c>
       <c r="B21" t="n">
         <v>78967</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502479</v>
+        <v>502125</v>
       </c>
       <c r="R21" t="n">
-        <v>6761918</v>
+        <v>6762284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703156</v>
+        <v>125703119</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502540</v>
+        <v>502363</v>
       </c>
       <c r="R22" t="n">
-        <v>6761708</v>
+        <v>6761945</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703119</v>
+        <v>125703032</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>97215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502363</v>
+        <v>502146</v>
       </c>
       <c r="R23" t="n">
-        <v>6761945</v>
+        <v>6762231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703032</v>
+        <v>125703156</v>
       </c>
       <c r="B25" t="n">
-        <v>97208</v>
+        <v>78967</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502146</v>
+        <v>502540</v>
       </c>
       <c r="R25" t="n">
-        <v>6762231</v>
+        <v>6761708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2971,12 +2971,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703152</v>
+        <v>125703124</v>
       </c>
       <c r="B27" t="n">
         <v>78967</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502468</v>
+        <v>502334</v>
       </c>
       <c r="R27" t="n">
-        <v>6761842</v>
+        <v>6762017</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703124</v>
+        <v>125703118</v>
       </c>
       <c r="B28" t="n">
         <v>78967</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502334</v>
+        <v>502506</v>
       </c>
       <c r="R28" t="n">
-        <v>6762017</v>
+        <v>6761695</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703118</v>
+        <v>125703152</v>
       </c>
       <c r="B29" t="n">
         <v>78967</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502506</v>
+        <v>502468</v>
       </c>
       <c r="R29" t="n">
-        <v>6761695</v>
+        <v>6761842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,7 +3488,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703115</v>
+        <v>125703143</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>502512</v>
+        <v>502397</v>
       </c>
       <c r="R31" t="n">
-        <v>6761663</v>
+        <v>6761934</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703143</v>
+        <v>125703115</v>
       </c>
       <c r="B32" t="n">
         <v>78967</v>
@@ -3620,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>502397</v>
+        <v>502512</v>
       </c>
       <c r="R32" t="n">
-        <v>6761934</v>
+        <v>6761663</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703113</v>
+        <v>125703126</v>
       </c>
       <c r="B35" t="n">
         <v>78967</v>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502516</v>
+        <v>502300</v>
       </c>
       <c r="R35" t="n">
-        <v>6761621</v>
+        <v>6762030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703110</v>
+        <v>125703113</v>
       </c>
       <c r="B36" t="n">
         <v>78967</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502509</v>
+        <v>502516</v>
       </c>
       <c r="R36" t="n">
-        <v>6761598</v>
+        <v>6761621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703147</v>
+        <v>125703136</v>
       </c>
       <c r="B37" t="n">
         <v>78967</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502460</v>
+        <v>502437</v>
       </c>
       <c r="R37" t="n">
-        <v>6761921</v>
+        <v>6761976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703126</v>
+        <v>125703131</v>
       </c>
       <c r="B38" t="n">
         <v>78967</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502300</v>
+        <v>502297</v>
       </c>
       <c r="R38" t="n">
-        <v>6762030</v>
+        <v>6762055</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703136</v>
+        <v>125703147</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502437</v>
+        <v>502460</v>
       </c>
       <c r="R39" t="n">
-        <v>6761976</v>
+        <v>6761921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703131</v>
+        <v>125703110</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502297</v>
+        <v>502509</v>
       </c>
       <c r="R41" t="n">
-        <v>6762055</v>
+        <v>6761598</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703043</v>
+        <v>125703050</v>
       </c>
       <c r="B50" t="n">
         <v>78967</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502173</v>
+        <v>502130</v>
       </c>
       <c r="R50" t="n">
-        <v>6762170</v>
+        <v>6762292</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125703130</v>
+        <v>125703043</v>
       </c>
       <c r="B51" t="n">
         <v>78967</v>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502291</v>
+        <v>502173</v>
       </c>
       <c r="R51" t="n">
-        <v>6762055</v>
+        <v>6762170</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703050</v>
+        <v>125703130</v>
       </c>
       <c r="B52" t="n">
         <v>78967</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502130</v>
+        <v>502291</v>
       </c>
       <c r="R52" t="n">
-        <v>6762292</v>
+        <v>6762055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703112</v>
+        <v>125703037</v>
       </c>
       <c r="B57" t="n">
         <v>78967</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502515</v>
+        <v>502275</v>
       </c>
       <c r="R57" t="n">
-        <v>6761615</v>
+        <v>6762145</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6107,7 +6107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703037</v>
+        <v>125703044</v>
       </c>
       <c r="B58" t="n">
         <v>78967</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502275</v>
+        <v>502165</v>
       </c>
       <c r="R58" t="n">
-        <v>6762145</v>
+        <v>6762230</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703138</v>
+        <v>125703112</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502374</v>
+        <v>502515</v>
       </c>
       <c r="R59" t="n">
-        <v>6762057</v>
+        <v>6761615</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703150</v>
+        <v>125703138</v>
       </c>
       <c r="B60" t="n">
         <v>78967</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502446</v>
+        <v>502374</v>
       </c>
       <c r="R60" t="n">
-        <v>6761867</v>
+        <v>6762057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703044</v>
+        <v>125703150</v>
       </c>
       <c r="B61" t="n">
         <v>78967</v>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502165</v>
+        <v>502446</v>
       </c>
       <c r="R61" t="n">
-        <v>6762230</v>
+        <v>6761867</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6883,7 +6883,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703127</v>
+        <v>125703129</v>
       </c>
       <c r="B66" t="n">
         <v>78967</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502294</v>
+        <v>502289</v>
       </c>
       <c r="R66" t="n">
-        <v>6762030</v>
+        <v>6762038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125703129</v>
+        <v>125703127</v>
       </c>
       <c r="B67" t="n">
         <v>78967</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502289</v>
+        <v>502294</v>
       </c>
       <c r="R67" t="n">
-        <v>6762038</v>
+        <v>6762030</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B69" t="n">
         <v>78967</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R69" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B70" t="n">
         <v>78967</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R70" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704411</v>
+        <v>125704224</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502100</v>
+        <v>502310</v>
       </c>
       <c r="R71" t="n">
-        <v>6762414</v>
+        <v>6762110</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7465,7 +7465,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704224</v>
+        <v>125704051</v>
       </c>
       <c r="B72" t="n">
         <v>78967</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502310</v>
+        <v>502592</v>
       </c>
       <c r="R72" t="n">
-        <v>6762110</v>
+        <v>6761383</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704097</v>
+        <v>125704248</v>
       </c>
       <c r="B73" t="n">
         <v>78967</v>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502069</v>
+        <v>502091</v>
       </c>
       <c r="R73" t="n">
-        <v>6762427</v>
+        <v>6762321</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7659,7 +7659,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704248</v>
+        <v>125704097</v>
       </c>
       <c r="B74" t="n">
         <v>78967</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502091</v>
+        <v>502069</v>
       </c>
       <c r="R74" t="n">
-        <v>6762321</v>
+        <v>6762427</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,7 +7756,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704051</v>
+        <v>125704411</v>
       </c>
       <c r="B75" t="n">
         <v>78967</v>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502592</v>
+        <v>502100</v>
       </c>
       <c r="R75" t="n">
-        <v>6761383</v>
+        <v>6762414</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7853,7 +7853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125704416</v>
+        <v>125703063</v>
       </c>
       <c r="B76" t="n">
         <v>78967</v>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502139</v>
+        <v>502048</v>
       </c>
       <c r="R76" t="n">
-        <v>6762359</v>
+        <v>6762403</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125703063</v>
+        <v>125704416</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502048</v>
+        <v>502139</v>
       </c>
       <c r="R77" t="n">
-        <v>6762403</v>
+        <v>6762359</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704414</v>
+        <v>125704102</v>
       </c>
       <c r="B80" t="n">
         <v>78967</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703128</v>
+        <v>125703142</v>
       </c>
       <c r="B2" t="n">
         <v>78967</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502289</v>
+        <v>502396</v>
       </c>
       <c r="R2" t="n">
-        <v>6762035</v>
+        <v>6761943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703141</v>
+        <v>125703036</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502408</v>
+        <v>502277</v>
       </c>
       <c r="R3" t="n">
-        <v>6761981</v>
+        <v>6762122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703034</v>
+        <v>125703128</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502119</v>
+        <v>502289</v>
       </c>
       <c r="R4" t="n">
-        <v>6762355</v>
+        <v>6762035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703117</v>
+        <v>125703141</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502502</v>
+        <v>502408</v>
       </c>
       <c r="R5" t="n">
-        <v>6761684</v>
+        <v>6761981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703142</v>
+        <v>125703034</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502396</v>
+        <v>502119</v>
       </c>
       <c r="R6" t="n">
-        <v>6761943</v>
+        <v>6762355</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703036</v>
+        <v>125703117</v>
       </c>
       <c r="B7" t="n">
         <v>78967</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502277</v>
+        <v>502502</v>
       </c>
       <c r="R7" t="n">
-        <v>6762122</v>
+        <v>6761684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703152</v>
+        <v>125703133</v>
       </c>
       <c r="B29" t="n">
         <v>78967</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502468</v>
+        <v>502464</v>
       </c>
       <c r="R29" t="n">
-        <v>6761842</v>
+        <v>6761949</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703133</v>
+        <v>125703152</v>
       </c>
       <c r="B30" t="n">
         <v>78967</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502464</v>
+        <v>502468</v>
       </c>
       <c r="R30" t="n">
-        <v>6761949</v>
+        <v>6761842</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -7853,7 +7853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125703063</v>
+        <v>125704416</v>
       </c>
       <c r="B76" t="n">
         <v>78967</v>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502048</v>
+        <v>502139</v>
       </c>
       <c r="R76" t="n">
-        <v>6762403</v>
+        <v>6762359</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125704416</v>
+        <v>125703063</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502139</v>
+        <v>502048</v>
       </c>
       <c r="R77" t="n">
-        <v>6762359</v>
+        <v>6762403</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B95" t="n">
         <v>78967</v>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R95" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,7 +9793,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B96" t="n">
         <v>78967</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R96" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -5331,7 +5331,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703050</v>
+        <v>125703130</v>
       </c>
       <c r="B50" t="n">
         <v>78967</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502130</v>
+        <v>502291</v>
       </c>
       <c r="R50" t="n">
-        <v>6762292</v>
+        <v>6762055</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703130</v>
+        <v>125703050</v>
       </c>
       <c r="B52" t="n">
         <v>78967</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502291</v>
+        <v>502130</v>
       </c>
       <c r="R52" t="n">
-        <v>6762055</v>
+        <v>6762292</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5913,7 +5913,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703146</v>
+        <v>125703112</v>
       </c>
       <c r="B56" t="n">
         <v>78967</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502447</v>
+        <v>502515</v>
       </c>
       <c r="R56" t="n">
-        <v>6761914</v>
+        <v>6761615</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703037</v>
+        <v>125703138</v>
       </c>
       <c r="B57" t="n">
         <v>78967</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502275</v>
+        <v>502374</v>
       </c>
       <c r="R57" t="n">
-        <v>6762145</v>
+        <v>6762057</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6107,7 +6107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703044</v>
+        <v>125703150</v>
       </c>
       <c r="B58" t="n">
         <v>78967</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502165</v>
+        <v>502446</v>
       </c>
       <c r="R58" t="n">
-        <v>6762230</v>
+        <v>6761867</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703112</v>
+        <v>125703146</v>
       </c>
       <c r="B59" t="n">
         <v>78967</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502515</v>
+        <v>502447</v>
       </c>
       <c r="R59" t="n">
-        <v>6761615</v>
+        <v>6761914</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703138</v>
+        <v>125703037</v>
       </c>
       <c r="B60" t="n">
         <v>78967</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502374</v>
+        <v>502275</v>
       </c>
       <c r="R60" t="n">
-        <v>6762057</v>
+        <v>6762145</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6398,7 +6398,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703150</v>
+        <v>125703044</v>
       </c>
       <c r="B61" t="n">
         <v>78967</v>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502446</v>
+        <v>502165</v>
       </c>
       <c r="R61" t="n">
-        <v>6761867</v>
+        <v>6762230</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7368,7 +7368,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704224</v>
+        <v>125704248</v>
       </c>
       <c r="B71" t="n">
         <v>78967</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502310</v>
+        <v>502091</v>
       </c>
       <c r="R71" t="n">
-        <v>6762110</v>
+        <v>6762321</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704051</v>
+        <v>125704224</v>
       </c>
       <c r="B72" t="n">
         <v>78967</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502592</v>
+        <v>502310</v>
       </c>
       <c r="R72" t="n">
-        <v>6761383</v>
+        <v>6762110</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704248</v>
+        <v>125704051</v>
       </c>
       <c r="B73" t="n">
         <v>78967</v>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502091</v>
+        <v>502592</v>
       </c>
       <c r="R73" t="n">
-        <v>6762321</v>
+        <v>6761383</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7853,7 +7853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125704416</v>
+        <v>125703063</v>
       </c>
       <c r="B76" t="n">
         <v>78967</v>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502139</v>
+        <v>502048</v>
       </c>
       <c r="R76" t="n">
-        <v>6762359</v>
+        <v>6762403</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125703063</v>
+        <v>125704416</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502048</v>
+        <v>502139</v>
       </c>
       <c r="R77" t="n">
-        <v>6762403</v>
+        <v>6762359</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703142</v>
+        <v>125703036</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502396</v>
+        <v>502277</v>
       </c>
       <c r="R2" t="n">
-        <v>6761943</v>
+        <v>6762122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703036</v>
+        <v>125703141</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502277</v>
+        <v>502408</v>
       </c>
       <c r="R3" t="n">
-        <v>6762122</v>
+        <v>6761981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703128</v>
+        <v>125703142</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502289</v>
+        <v>502396</v>
       </c>
       <c r="R4" t="n">
-        <v>6762035</v>
+        <v>6761943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703141</v>
+        <v>125703128</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502408</v>
+        <v>502289</v>
       </c>
       <c r="R5" t="n">
-        <v>6761981</v>
+        <v>6762035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>125703034</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125703117</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125703137</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703121</v>
+        <v>125703109</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502337</v>
+        <v>502522</v>
       </c>
       <c r="R9" t="n">
-        <v>6761987</v>
+        <v>6761590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703116</v>
+        <v>125703121</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502499</v>
+        <v>502337</v>
       </c>
       <c r="R10" t="n">
-        <v>6761670</v>
+        <v>6761987</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703109</v>
+        <v>125703116</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502522</v>
+        <v>502499</v>
       </c>
       <c r="R11" t="n">
-        <v>6761590</v>
+        <v>6761670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1648,7 @@
         <v>125703134</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125703052</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125703155</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703158</v>
+        <v>125703038</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502561</v>
+        <v>502265</v>
       </c>
       <c r="R15" t="n">
-        <v>6761653</v>
+        <v>6762114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703035</v>
+        <v>125703158</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502289</v>
+        <v>502561</v>
       </c>
       <c r="R16" t="n">
-        <v>6762117</v>
+        <v>6761653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703038</v>
+        <v>125703140</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502265</v>
+        <v>502377</v>
       </c>
       <c r="R17" t="n">
-        <v>6762114</v>
+        <v>6761992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703140</v>
+        <v>125703035</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502377</v>
+        <v>502289</v>
       </c>
       <c r="R18" t="n">
-        <v>6761992</v>
+        <v>6762117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2327,7 +2327,7 @@
         <v>125703153</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703148</v>
+        <v>125703049</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502479</v>
+        <v>502125</v>
       </c>
       <c r="R20" t="n">
-        <v>6761918</v>
+        <v>6762284</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125703049</v>
+        <v>125703148</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502125</v>
+        <v>502479</v>
       </c>
       <c r="R21" t="n">
-        <v>6762284</v>
+        <v>6761918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703119</v>
+        <v>125703125</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502363</v>
+        <v>502314</v>
       </c>
       <c r="R22" t="n">
-        <v>6761945</v>
+        <v>6762028</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,32 +2712,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703032</v>
+        <v>125703156</v>
       </c>
       <c r="B23" t="n">
-        <v>97215</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502146</v>
+        <v>502540</v>
       </c>
       <c r="R23" t="n">
-        <v>6762231</v>
+        <v>6761708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703111</v>
+        <v>125703119</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502516</v>
+        <v>502363</v>
       </c>
       <c r="R24" t="n">
-        <v>6761612</v>
+        <v>6761945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703156</v>
+        <v>125703111</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502540</v>
+        <v>502516</v>
       </c>
       <c r="R25" t="n">
-        <v>6761708</v>
+        <v>6761612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703125</v>
+        <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>97218</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502314</v>
+        <v>502146</v>
       </c>
       <c r="R26" t="n">
-        <v>6762028</v>
+        <v>6762231</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703124</v>
+        <v>125703152</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502334</v>
+        <v>502468</v>
       </c>
       <c r="R27" t="n">
-        <v>6762017</v>
+        <v>6761842</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703118</v>
+        <v>125703124</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502506</v>
+        <v>502334</v>
       </c>
       <c r="R28" t="n">
-        <v>6761695</v>
+        <v>6762017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703133</v>
+        <v>125703118</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502464</v>
+        <v>502506</v>
       </c>
       <c r="R29" t="n">
-        <v>6761949</v>
+        <v>6761695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703152</v>
+        <v>125703133</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502468</v>
+        <v>502464</v>
       </c>
       <c r="R30" t="n">
-        <v>6761842</v>
+        <v>6761949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>125703143</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>125703115</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>125703157</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>125703123</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703126</v>
+        <v>125703136</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502300</v>
+        <v>502437</v>
       </c>
       <c r="R35" t="n">
-        <v>6762030</v>
+        <v>6761976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703113</v>
+        <v>125703110</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502516</v>
+        <v>502509</v>
       </c>
       <c r="R36" t="n">
-        <v>6761621</v>
+        <v>6761598</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703136</v>
+        <v>125703147</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502437</v>
+        <v>502460</v>
       </c>
       <c r="R37" t="n">
-        <v>6761976</v>
+        <v>6761921</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703131</v>
+        <v>125703126</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502297</v>
+        <v>502300</v>
       </c>
       <c r="R38" t="n">
-        <v>6762055</v>
+        <v>6762030</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703147</v>
+        <v>125703113</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502460</v>
+        <v>502516</v>
       </c>
       <c r="R39" t="n">
-        <v>6761921</v>
+        <v>6761621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,7 +4364,7 @@
         <v>125703033</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703110</v>
+        <v>125703131</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502509</v>
+        <v>502297</v>
       </c>
       <c r="R41" t="n">
-        <v>6761598</v>
+        <v>6762055</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4558,7 +4558,7 @@
         <v>125703051</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4652,10 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703042</v>
+        <v>125703139</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502201</v>
+        <v>502377</v>
       </c>
       <c r="R43" t="n">
-        <v>6762164</v>
+        <v>6762023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4749,10 +4749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703139</v>
+        <v>125703132</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502377</v>
+        <v>502329</v>
       </c>
       <c r="R44" t="n">
-        <v>6762023</v>
+        <v>6762061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703132</v>
+        <v>125703160</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502329</v>
+        <v>502555</v>
       </c>
       <c r="R45" t="n">
-        <v>6762061</v>
+        <v>6761580</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703114</v>
+        <v>125703042</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502523</v>
+        <v>502201</v>
       </c>
       <c r="R46" t="n">
-        <v>6761654</v>
+        <v>6762164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5040,10 +5040,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703160</v>
+        <v>125703114</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502555</v>
+        <v>502523</v>
       </c>
       <c r="R47" t="n">
-        <v>6761580</v>
+        <v>6761654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703047</v>
+        <v>125703039</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502134</v>
+        <v>502249</v>
       </c>
       <c r="R48" t="n">
-        <v>6762272</v>
+        <v>6762132</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125703039</v>
+        <v>125703047</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502249</v>
+        <v>502134</v>
       </c>
       <c r="R49" t="n">
-        <v>6762132</v>
+        <v>6762272</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703130</v>
+        <v>125703050</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502291</v>
+        <v>502130</v>
       </c>
       <c r="R50" t="n">
-        <v>6762055</v>
+        <v>6762292</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5431,7 +5431,7 @@
         <v>125703043</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703050</v>
+        <v>125703130</v>
       </c>
       <c r="B52" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502130</v>
+        <v>502291</v>
       </c>
       <c r="R52" t="n">
-        <v>6762292</v>
+        <v>6762055</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5625,7 +5625,7 @@
         <v>125703122</v>
       </c>
       <c r="B53" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>125703149</v>
       </c>
       <c r="B54" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>125703145</v>
       </c>
       <c r="B55" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703112</v>
+        <v>125703037</v>
       </c>
       <c r="B56" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502515</v>
+        <v>502275</v>
       </c>
       <c r="R56" t="n">
-        <v>6761615</v>
+        <v>6762145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6010,10 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703138</v>
+        <v>125703044</v>
       </c>
       <c r="B57" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502374</v>
+        <v>502165</v>
       </c>
       <c r="R57" t="n">
-        <v>6762057</v>
+        <v>6762230</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703150</v>
+        <v>125703146</v>
       </c>
       <c r="B58" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502446</v>
+        <v>502447</v>
       </c>
       <c r="R58" t="n">
-        <v>6761867</v>
+        <v>6761914</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703146</v>
+        <v>125703112</v>
       </c>
       <c r="B59" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502447</v>
+        <v>502515</v>
       </c>
       <c r="R59" t="n">
-        <v>6761914</v>
+        <v>6761615</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703037</v>
+        <v>125703138</v>
       </c>
       <c r="B60" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502275</v>
+        <v>502374</v>
       </c>
       <c r="R60" t="n">
-        <v>6762145</v>
+        <v>6762057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703044</v>
+        <v>125703150</v>
       </c>
       <c r="B61" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502165</v>
+        <v>502446</v>
       </c>
       <c r="R61" t="n">
-        <v>6762230</v>
+        <v>6761867</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6498,7 +6498,7 @@
         <v>125703041</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>125703135</v>
       </c>
       <c r="B63" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>125703045</v>
       </c>
       <c r="B64" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>125703120</v>
       </c>
       <c r="B65" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6883,10 +6883,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703129</v>
+        <v>125703154</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502289</v>
+        <v>502490</v>
       </c>
       <c r="R66" t="n">
-        <v>6762038</v>
+        <v>6761791</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6983,7 +6983,7 @@
         <v>125703127</v>
       </c>
       <c r="B67" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125703154</v>
+        <v>125703129</v>
       </c>
       <c r="B68" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>502490</v>
+        <v>502289</v>
       </c>
       <c r="R68" t="n">
-        <v>6761791</v>
+        <v>6762038</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7174,10 +7174,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R69" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R70" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704248</v>
+        <v>125704411</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502091</v>
+        <v>502100</v>
       </c>
       <c r="R71" t="n">
-        <v>6762321</v>
+        <v>6762414</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7465,10 +7465,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704224</v>
+        <v>125704051</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502310</v>
+        <v>502592</v>
       </c>
       <c r="R72" t="n">
-        <v>6762110</v>
+        <v>6761383</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,10 +7562,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704051</v>
+        <v>125704248</v>
       </c>
       <c r="B73" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502592</v>
+        <v>502091</v>
       </c>
       <c r="R73" t="n">
-        <v>6761383</v>
+        <v>6762321</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7659,10 +7659,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704097</v>
+        <v>125704224</v>
       </c>
       <c r="B74" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502069</v>
+        <v>502310</v>
       </c>
       <c r="R74" t="n">
-        <v>6762427</v>
+        <v>6762110</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,10 +7756,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704411</v>
+        <v>125704097</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502100</v>
+        <v>502069</v>
       </c>
       <c r="R75" t="n">
-        <v>6762414</v>
+        <v>6762427</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>125703063</v>
       </c>
       <c r="B76" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>125704416</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125704362</v>
+        <v>125703055</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>502594</v>
+        <v>502094</v>
       </c>
       <c r="R78" t="n">
-        <v>6761374</v>
+        <v>6762325</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125703055</v>
+        <v>125704362</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>502094</v>
+        <v>502594</v>
       </c>
       <c r="R79" t="n">
-        <v>6762325</v>
+        <v>6761374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704102</v>
+        <v>125704414</v>
       </c>
       <c r="B80" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>125703074</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>125703057</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>125704359</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125703061</v>
+        <v>125703071</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>502072</v>
+        <v>502078</v>
       </c>
       <c r="R84" t="n">
-        <v>6762386</v>
+        <v>6762412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125703071</v>
+        <v>125703061</v>
       </c>
       <c r="B85" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502078</v>
+        <v>502072</v>
       </c>
       <c r="R85" t="n">
-        <v>6762412</v>
+        <v>6762386</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
         <v>125703067</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>125704225</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>125703073</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>125704053</v>
       </c>
       <c r="B89" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>125703062</v>
       </c>
       <c r="B90" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>125703056</v>
       </c>
       <c r="B91" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>125703066</v>
       </c>
       <c r="B92" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>125703064</v>
       </c>
       <c r="B93" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125704055</v>
+        <v>125704222</v>
       </c>
       <c r="B94" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9696,10 +9696,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B95" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R95" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R96" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9893,7 +9893,7 @@
         <v>125703060</v>
       </c>
       <c r="B97" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>125703058</v>
       </c>
       <c r="B98" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703125</v>
+        <v>125703032</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>97218</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502314</v>
+        <v>502146</v>
       </c>
       <c r="R22" t="n">
-        <v>6762028</v>
+        <v>6762231</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703156</v>
+        <v>125703125</v>
       </c>
       <c r="B23" t="n">
         <v>78968</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502540</v>
+        <v>502314</v>
       </c>
       <c r="R23" t="n">
-        <v>6761708</v>
+        <v>6762028</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703119</v>
+        <v>125703156</v>
       </c>
       <c r="B24" t="n">
         <v>78968</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502363</v>
+        <v>502540</v>
       </c>
       <c r="R24" t="n">
-        <v>6761945</v>
+        <v>6761708</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703111</v>
+        <v>125703119</v>
       </c>
       <c r="B25" t="n">
         <v>78968</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502516</v>
+        <v>502363</v>
       </c>
       <c r="R25" t="n">
-        <v>6761612</v>
+        <v>6761945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703032</v>
+        <v>125703111</v>
       </c>
       <c r="B26" t="n">
-        <v>97218</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502146</v>
+        <v>502516</v>
       </c>
       <c r="R26" t="n">
-        <v>6762231</v>
+        <v>6761612</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703051</v>
+        <v>125703132</v>
       </c>
       <c r="B42" t="n">
         <v>78968</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502107</v>
+        <v>502329</v>
       </c>
       <c r="R42" t="n">
-        <v>6762317</v>
+        <v>6762061</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,7 +4652,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703139</v>
+        <v>125703160</v>
       </c>
       <c r="B43" t="n">
         <v>78968</v>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502377</v>
+        <v>502555</v>
       </c>
       <c r="R43" t="n">
-        <v>6762023</v>
+        <v>6761580</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703132</v>
+        <v>125703051</v>
       </c>
       <c r="B44" t="n">
         <v>78968</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502329</v>
+        <v>502107</v>
       </c>
       <c r="R44" t="n">
-        <v>6762061</v>
+        <v>6762317</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703160</v>
+        <v>125703139</v>
       </c>
       <c r="B45" t="n">
         <v>78968</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502555</v>
+        <v>502377</v>
       </c>
       <c r="R45" t="n">
-        <v>6761580</v>
+        <v>6762023</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703037</v>
+        <v>125703044</v>
       </c>
       <c r="B56" t="n">
         <v>78968</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502275</v>
+        <v>502165</v>
       </c>
       <c r="R56" t="n">
-        <v>6762145</v>
+        <v>6762230</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703044</v>
+        <v>125703037</v>
       </c>
       <c r="B57" t="n">
         <v>78968</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502165</v>
+        <v>502275</v>
       </c>
       <c r="R57" t="n">
-        <v>6762230</v>
+        <v>6762145</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703154</v>
+        <v>125703129</v>
       </c>
       <c r="B66" t="n">
         <v>78968</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502490</v>
+        <v>502289</v>
       </c>
       <c r="R66" t="n">
-        <v>6761791</v>
+        <v>6762038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125703127</v>
+        <v>125703154</v>
       </c>
       <c r="B67" t="n">
         <v>78968</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502294</v>
+        <v>502490</v>
       </c>
       <c r="R67" t="n">
-        <v>6762030</v>
+        <v>6761791</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125703129</v>
+        <v>125703127</v>
       </c>
       <c r="B68" t="n">
         <v>78968</v>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>502289</v>
+        <v>502294</v>
       </c>
       <c r="R68" t="n">
-        <v>6762038</v>
+        <v>6762030</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703036</v>
+        <v>125703142</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502277</v>
+        <v>502396</v>
       </c>
       <c r="R2" t="n">
-        <v>6762122</v>
+        <v>6761943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703141</v>
+        <v>125703117</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502408</v>
+        <v>502502</v>
       </c>
       <c r="R3" t="n">
-        <v>6761981</v>
+        <v>6761684</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703142</v>
+        <v>125703036</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502396</v>
+        <v>502277</v>
       </c>
       <c r="R4" t="n">
-        <v>6761943</v>
+        <v>6762122</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,7 +969,7 @@
         <v>125703128</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703034</v>
+        <v>125703141</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502119</v>
+        <v>502408</v>
       </c>
       <c r="R6" t="n">
-        <v>6762355</v>
+        <v>6761981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703117</v>
+        <v>125703034</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502502</v>
+        <v>502119</v>
       </c>
       <c r="R7" t="n">
-        <v>6761684</v>
+        <v>6762355</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,7 +1260,7 @@
         <v>125703137</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703109</v>
+        <v>125703134</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502522</v>
+        <v>502457</v>
       </c>
       <c r="R9" t="n">
-        <v>6761590</v>
+        <v>6761959</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703121</v>
+        <v>125703116</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502337</v>
+        <v>502499</v>
       </c>
       <c r="R10" t="n">
-        <v>6761987</v>
+        <v>6761670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703116</v>
+        <v>125703109</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502499</v>
+        <v>502522</v>
       </c>
       <c r="R11" t="n">
-        <v>6761670</v>
+        <v>6761590</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703134</v>
+        <v>125703121</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502457</v>
+        <v>502337</v>
       </c>
       <c r="R12" t="n">
-        <v>6761959</v>
+        <v>6761987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703052</v>
+        <v>125703038</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502090</v>
+        <v>502265</v>
       </c>
       <c r="R13" t="n">
-        <v>6762313</v>
+        <v>6762114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703155</v>
+        <v>125703052</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502545</v>
+        <v>502090</v>
       </c>
       <c r="R14" t="n">
-        <v>6761701</v>
+        <v>6762313</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703038</v>
+        <v>125703158</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502265</v>
+        <v>502561</v>
       </c>
       <c r="R15" t="n">
-        <v>6762114</v>
+        <v>6761653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R16" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703140</v>
+        <v>125703155</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502377</v>
+        <v>502545</v>
       </c>
       <c r="R17" t="n">
-        <v>6761992</v>
+        <v>6761701</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>125703035</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125703153</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703049</v>
+        <v>125703148</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502125</v>
+        <v>502479</v>
       </c>
       <c r="R20" t="n">
-        <v>6762284</v>
+        <v>6761918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2486,12 +2486,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125703148</v>
+        <v>125703049</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502479</v>
+        <v>502125</v>
       </c>
       <c r="R21" t="n">
-        <v>6761918</v>
+        <v>6762284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703032</v>
+        <v>125703156</v>
       </c>
       <c r="B22" t="n">
-        <v>97218</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502146</v>
+        <v>502540</v>
       </c>
       <c r="R22" t="n">
-        <v>6762231</v>
+        <v>6761708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703125</v>
+        <v>125703119</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502314</v>
+        <v>502363</v>
       </c>
       <c r="R23" t="n">
-        <v>6762028</v>
+        <v>6761945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703156</v>
+        <v>125703111</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502540</v>
+        <v>502516</v>
       </c>
       <c r="R24" t="n">
-        <v>6761708</v>
+        <v>6761612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703119</v>
+        <v>125703125</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502363</v>
+        <v>502314</v>
       </c>
       <c r="R25" t="n">
-        <v>6761945</v>
+        <v>6762028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703111</v>
+        <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>97222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502516</v>
+        <v>502146</v>
       </c>
       <c r="R26" t="n">
-        <v>6761612</v>
+        <v>6762231</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3103,7 +3103,7 @@
         <v>125703152</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125703124</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>125703118</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         <v>125703133</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>125703143</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>125703115</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>125703157</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>125703123</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703136</v>
+        <v>125703126</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502437</v>
+        <v>502300</v>
       </c>
       <c r="R35" t="n">
-        <v>6761976</v>
+        <v>6762030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3976,7 +3976,7 @@
         <v>125703110</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>125703147</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703126</v>
+        <v>125703113</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502300</v>
+        <v>502516</v>
       </c>
       <c r="R38" t="n">
-        <v>6762030</v>
+        <v>6761621</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703113</v>
+        <v>125703136</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502516</v>
+        <v>502437</v>
       </c>
       <c r="R39" t="n">
-        <v>6761621</v>
+        <v>6761976</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4364,7 +4364,7 @@
         <v>125703033</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
         <v>125703131</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703132</v>
+        <v>125703042</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502329</v>
+        <v>502201</v>
       </c>
       <c r="R42" t="n">
-        <v>6762061</v>
+        <v>6762164</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,10 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703160</v>
+        <v>125703139</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502555</v>
+        <v>502377</v>
       </c>
       <c r="R43" t="n">
-        <v>6761580</v>
+        <v>6762023</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,10 +4749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703051</v>
+        <v>125703132</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502107</v>
+        <v>502329</v>
       </c>
       <c r="R44" t="n">
-        <v>6762317</v>
+        <v>6762061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703139</v>
+        <v>125703051</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502377</v>
+        <v>502107</v>
       </c>
       <c r="R45" t="n">
-        <v>6762023</v>
+        <v>6762317</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703042</v>
+        <v>125703114</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502201</v>
+        <v>502523</v>
       </c>
       <c r="R46" t="n">
-        <v>6762164</v>
+        <v>6761654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5040,10 +5040,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703114</v>
+        <v>125703160</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502523</v>
+        <v>502555</v>
       </c>
       <c r="R47" t="n">
-        <v>6761654</v>
+        <v>6761580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703039</v>
+        <v>125703047</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502249</v>
+        <v>502134</v>
       </c>
       <c r="R48" t="n">
-        <v>6762132</v>
+        <v>6762272</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125703047</v>
+        <v>125703039</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502134</v>
+        <v>502249</v>
       </c>
       <c r="R49" t="n">
-        <v>6762272</v>
+        <v>6762132</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5334,7 +5334,7 @@
         <v>125703050</v>
       </c>
       <c r="B50" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>125703043</v>
       </c>
       <c r="B51" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>125703130</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>125703122</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>125703149</v>
       </c>
       <c r="B54" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>125703145</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703044</v>
+        <v>125703138</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502165</v>
+        <v>502374</v>
       </c>
       <c r="R56" t="n">
-        <v>6762230</v>
+        <v>6762057</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6010,10 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703037</v>
+        <v>125703150</v>
       </c>
       <c r="B57" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502275</v>
+        <v>502446</v>
       </c>
       <c r="R57" t="n">
-        <v>6762145</v>
+        <v>6761867</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6110,7 +6110,7 @@
         <v>125703146</v>
       </c>
       <c r="B58" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>125703112</v>
       </c>
       <c r="B59" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703138</v>
+        <v>125703037</v>
       </c>
       <c r="B60" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502374</v>
+        <v>502275</v>
       </c>
       <c r="R60" t="n">
-        <v>6762057</v>
+        <v>6762145</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703150</v>
+        <v>125703044</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502446</v>
+        <v>502165</v>
       </c>
       <c r="R61" t="n">
-        <v>6761867</v>
+        <v>6762230</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6498,7 +6498,7 @@
         <v>125703041</v>
       </c>
       <c r="B62" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>125703135</v>
       </c>
       <c r="B63" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>125703045</v>
       </c>
       <c r="B64" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>125703120</v>
       </c>
       <c r="B65" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>125703129</v>
       </c>
       <c r="B66" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>125703154</v>
       </c>
       <c r="B67" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>125703127</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>125704103</v>
       </c>
       <c r="B69" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>125703069</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>125704411</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704051</v>
+        <v>125704248</v>
       </c>
       <c r="B72" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502592</v>
+        <v>502091</v>
       </c>
       <c r="R72" t="n">
-        <v>6761383</v>
+        <v>6762321</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,10 +7562,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704248</v>
+        <v>125704224</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502091</v>
+        <v>502310</v>
       </c>
       <c r="R73" t="n">
-        <v>6762321</v>
+        <v>6762110</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704224</v>
+        <v>125704097</v>
       </c>
       <c r="B74" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502310</v>
+        <v>502069</v>
       </c>
       <c r="R74" t="n">
-        <v>6762110</v>
+        <v>6762427</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,10 +7756,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704097</v>
+        <v>125704051</v>
       </c>
       <c r="B75" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502069</v>
+        <v>502592</v>
       </c>
       <c r="R75" t="n">
-        <v>6762427</v>
+        <v>6761383</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7853,10 +7853,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125703063</v>
+        <v>125704416</v>
       </c>
       <c r="B76" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502048</v>
+        <v>502139</v>
       </c>
       <c r="R76" t="n">
-        <v>6762403</v>
+        <v>6762359</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7950,10 +7950,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125704416</v>
+        <v>125703063</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502139</v>
+        <v>502048</v>
       </c>
       <c r="R77" t="n">
-        <v>6762359</v>
+        <v>6762403</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125703055</v>
+        <v>125704362</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>502094</v>
+        <v>502594</v>
       </c>
       <c r="R78" t="n">
-        <v>6762325</v>
+        <v>6761374</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125704362</v>
+        <v>125703055</v>
       </c>
       <c r="B79" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>502594</v>
+        <v>502094</v>
       </c>
       <c r="R79" t="n">
-        <v>6761374</v>
+        <v>6762325</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704414</v>
+        <v>125704102</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>125703074</v>
       </c>
       <c r="B81" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>125703057</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>125704359</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>125703071</v>
       </c>
       <c r="B84" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>125703061</v>
       </c>
       <c r="B85" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>125703067</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8920,10 +8920,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125704225</v>
+        <v>125704053</v>
       </c>
       <c r="B87" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>502288</v>
+        <v>502305</v>
       </c>
       <c r="R87" t="n">
-        <v>6762074</v>
+        <v>6762092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9017,10 +9017,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125703073</v>
+        <v>125704225</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>502087</v>
+        <v>502288</v>
       </c>
       <c r="R88" t="n">
-        <v>6762398</v>
+        <v>6762074</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9114,10 +9114,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125704053</v>
+        <v>125703073</v>
       </c>
       <c r="B89" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>502305</v>
+        <v>502087</v>
       </c>
       <c r="R89" t="n">
-        <v>6762092</v>
+        <v>6762398</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9214,7 +9214,7 @@
         <v>125703062</v>
       </c>
       <c r="B90" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>125703056</v>
       </c>
       <c r="B91" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>125703066</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>125703064</v>
       </c>
       <c r="B93" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>125704222</v>
       </c>
       <c r="B94" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>125703068</v>
       </c>
       <c r="B95" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>125703059</v>
       </c>
       <c r="B96" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>125703060</v>
       </c>
       <c r="B97" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>125703058</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703156</v>
+        <v>125703032</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>97222</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502540</v>
+        <v>502146</v>
       </c>
       <c r="R22" t="n">
-        <v>6761708</v>
+        <v>6762231</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703119</v>
+        <v>125703156</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502363</v>
+        <v>502540</v>
       </c>
       <c r="R23" t="n">
-        <v>6761945</v>
+        <v>6761708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703111</v>
+        <v>125703119</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502516</v>
+        <v>502363</v>
       </c>
       <c r="R24" t="n">
-        <v>6761612</v>
+        <v>6761945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703125</v>
+        <v>125703111</v>
       </c>
       <c r="B25" t="n">
         <v>78972</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502314</v>
+        <v>502516</v>
       </c>
       <c r="R25" t="n">
-        <v>6762028</v>
+        <v>6761612</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703032</v>
+        <v>125703125</v>
       </c>
       <c r="B26" t="n">
-        <v>97222</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502146</v>
+        <v>502314</v>
       </c>
       <c r="R26" t="n">
-        <v>6762231</v>
+        <v>6762028</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703142</v>
+        <v>125703036</v>
       </c>
       <c r="B2" t="n">
         <v>78972</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502396</v>
+        <v>502277</v>
       </c>
       <c r="R2" t="n">
-        <v>6761943</v>
+        <v>6762122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703117</v>
+        <v>125703142</v>
       </c>
       <c r="B3" t="n">
         <v>78972</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502502</v>
+        <v>502396</v>
       </c>
       <c r="R3" t="n">
-        <v>6761684</v>
+        <v>6761943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703036</v>
+        <v>125703128</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502277</v>
+        <v>502289</v>
       </c>
       <c r="R4" t="n">
-        <v>6762122</v>
+        <v>6762035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703128</v>
+        <v>125703141</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502289</v>
+        <v>502408</v>
       </c>
       <c r="R5" t="n">
-        <v>6762035</v>
+        <v>6761981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703141</v>
+        <v>125703034</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502408</v>
+        <v>502119</v>
       </c>
       <c r="R6" t="n">
-        <v>6761981</v>
+        <v>6762355</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703034</v>
+        <v>125703117</v>
       </c>
       <c r="B7" t="n">
         <v>78972</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502119</v>
+        <v>502502</v>
       </c>
       <c r="R7" t="n">
-        <v>6762355</v>
+        <v>6761684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703134</v>
+        <v>125703109</v>
       </c>
       <c r="B9" t="n">
         <v>78972</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502457</v>
+        <v>502522</v>
       </c>
       <c r="R9" t="n">
-        <v>6761959</v>
+        <v>6761590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703116</v>
+        <v>125703134</v>
       </c>
       <c r="B10" t="n">
         <v>78972</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502499</v>
+        <v>502457</v>
       </c>
       <c r="R10" t="n">
-        <v>6761670</v>
+        <v>6761959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703109</v>
+        <v>125703121</v>
       </c>
       <c r="B11" t="n">
         <v>78972</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502522</v>
+        <v>502337</v>
       </c>
       <c r="R11" t="n">
-        <v>6761590</v>
+        <v>6761987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703121</v>
+        <v>125703116</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502337</v>
+        <v>502499</v>
       </c>
       <c r="R12" t="n">
-        <v>6761987</v>
+        <v>6761670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703052</v>
+        <v>125703155</v>
       </c>
       <c r="B14" t="n">
         <v>78972</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502090</v>
+        <v>502545</v>
       </c>
       <c r="R14" t="n">
-        <v>6762313</v>
+        <v>6761701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703155</v>
+        <v>125703052</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502545</v>
+        <v>502090</v>
       </c>
       <c r="R17" t="n">
-        <v>6761701</v>
+        <v>6762313</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125703153</v>
+        <v>125703049</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502484</v>
+        <v>502125</v>
       </c>
       <c r="R19" t="n">
-        <v>6761867</v>
+        <v>6762284</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703148</v>
+        <v>125703153</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502479</v>
+        <v>502484</v>
       </c>
       <c r="R20" t="n">
-        <v>6761918</v>
+        <v>6761867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125703049</v>
+        <v>125703148</v>
       </c>
       <c r="B21" t="n">
         <v>78972</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502125</v>
+        <v>502479</v>
       </c>
       <c r="R21" t="n">
-        <v>6762284</v>
+        <v>6761918</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703032</v>
+        <v>125703156</v>
       </c>
       <c r="B22" t="n">
-        <v>97222</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502146</v>
+        <v>502540</v>
       </c>
       <c r="R22" t="n">
-        <v>6762231</v>
+        <v>6761708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703156</v>
+        <v>125703119</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502540</v>
+        <v>502363</v>
       </c>
       <c r="R23" t="n">
-        <v>6761708</v>
+        <v>6761945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703119</v>
+        <v>125703125</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502363</v>
+        <v>502314</v>
       </c>
       <c r="R24" t="n">
-        <v>6761945</v>
+        <v>6762028</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703125</v>
+        <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>97223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>502314</v>
+        <v>502146</v>
       </c>
       <c r="R26" t="n">
-        <v>6762028</v>
+        <v>6762231</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703152</v>
+        <v>125703118</v>
       </c>
       <c r="B27" t="n">
         <v>78972</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502468</v>
+        <v>502506</v>
       </c>
       <c r="R27" t="n">
-        <v>6761842</v>
+        <v>6761695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703124</v>
+        <v>125703152</v>
       </c>
       <c r="B28" t="n">
         <v>78972</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502334</v>
+        <v>502468</v>
       </c>
       <c r="R28" t="n">
-        <v>6762017</v>
+        <v>6761842</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703118</v>
+        <v>125703124</v>
       </c>
       <c r="B29" t="n">
         <v>78972</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502506</v>
+        <v>502334</v>
       </c>
       <c r="R29" t="n">
-        <v>6761695</v>
+        <v>6762017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703126</v>
+        <v>125703113</v>
       </c>
       <c r="B35" t="n">
         <v>78972</v>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502300</v>
+        <v>502516</v>
       </c>
       <c r="R35" t="n">
-        <v>6762030</v>
+        <v>6761621</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703110</v>
+        <v>125703136</v>
       </c>
       <c r="B36" t="n">
         <v>78972</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502509</v>
+        <v>502437</v>
       </c>
       <c r="R36" t="n">
-        <v>6761598</v>
+        <v>6761976</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703147</v>
+        <v>125703033</v>
       </c>
       <c r="B37" t="n">
         <v>78972</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502460</v>
+        <v>502147</v>
       </c>
       <c r="R37" t="n">
-        <v>6761921</v>
+        <v>6762242</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703113</v>
+        <v>125703110</v>
       </c>
       <c r="B38" t="n">
         <v>78972</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502516</v>
+        <v>502509</v>
       </c>
       <c r="R38" t="n">
-        <v>6761621</v>
+        <v>6761598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703136</v>
+        <v>125703147</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502437</v>
+        <v>502460</v>
       </c>
       <c r="R39" t="n">
-        <v>6761976</v>
+        <v>6761921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703033</v>
+        <v>125703126</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502147</v>
+        <v>502300</v>
       </c>
       <c r="R40" t="n">
-        <v>6762242</v>
+        <v>6762030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4555,7 +4555,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703042</v>
+        <v>125703051</v>
       </c>
       <c r="B42" t="n">
         <v>78972</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502201</v>
+        <v>502107</v>
       </c>
       <c r="R42" t="n">
-        <v>6762164</v>
+        <v>6762317</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703139</v>
+        <v>125703132</v>
       </c>
       <c r="B43" t="n">
         <v>78972</v>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502377</v>
+        <v>502329</v>
       </c>
       <c r="R43" t="n">
-        <v>6762023</v>
+        <v>6762061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703132</v>
+        <v>125703139</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502329</v>
+        <v>502377</v>
       </c>
       <c r="R44" t="n">
-        <v>6762061</v>
+        <v>6762023</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703051</v>
+        <v>125703114</v>
       </c>
       <c r="B45" t="n">
         <v>78972</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502107</v>
+        <v>502523</v>
       </c>
       <c r="R45" t="n">
-        <v>6762317</v>
+        <v>6761654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4911,12 +4911,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4943,7 +4943,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703114</v>
+        <v>125703042</v>
       </c>
       <c r="B46" t="n">
         <v>78972</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502523</v>
+        <v>502201</v>
       </c>
       <c r="R46" t="n">
-        <v>6761654</v>
+        <v>6762164</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5137,7 +5137,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703047</v>
+        <v>125703039</v>
       </c>
       <c r="B48" t="n">
         <v>78972</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502134</v>
+        <v>502249</v>
       </c>
       <c r="R48" t="n">
-        <v>6762272</v>
+        <v>6762132</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125703039</v>
+        <v>125703047</v>
       </c>
       <c r="B49" t="n">
         <v>78972</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502249</v>
+        <v>502134</v>
       </c>
       <c r="R49" t="n">
-        <v>6762132</v>
+        <v>6762272</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125703043</v>
+        <v>125703130</v>
       </c>
       <c r="B51" t="n">
         <v>78972</v>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502173</v>
+        <v>502291</v>
       </c>
       <c r="R51" t="n">
-        <v>6762170</v>
+        <v>6762055</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703130</v>
+        <v>125703043</v>
       </c>
       <c r="B52" t="n">
         <v>78972</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502291</v>
+        <v>502173</v>
       </c>
       <c r="R52" t="n">
-        <v>6762055</v>
+        <v>6762170</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5590,12 +5590,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5913,7 +5913,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703138</v>
+        <v>125703146</v>
       </c>
       <c r="B56" t="n">
         <v>78972</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502374</v>
+        <v>502447</v>
       </c>
       <c r="R56" t="n">
-        <v>6762057</v>
+        <v>6761914</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703150</v>
+        <v>125703112</v>
       </c>
       <c r="B57" t="n">
         <v>78972</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502446</v>
+        <v>502515</v>
       </c>
       <c r="R57" t="n">
-        <v>6761867</v>
+        <v>6761615</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703146</v>
+        <v>125703037</v>
       </c>
       <c r="B58" t="n">
         <v>78972</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502447</v>
+        <v>502275</v>
       </c>
       <c r="R58" t="n">
-        <v>6761914</v>
+        <v>6762145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703112</v>
+        <v>125703138</v>
       </c>
       <c r="B59" t="n">
         <v>78972</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502515</v>
+        <v>502374</v>
       </c>
       <c r="R59" t="n">
-        <v>6761615</v>
+        <v>6762057</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6301,7 +6301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703037</v>
+        <v>125703150</v>
       </c>
       <c r="B60" t="n">
         <v>78972</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502275</v>
+        <v>502446</v>
       </c>
       <c r="R60" t="n">
-        <v>6762145</v>
+        <v>6761867</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6495,7 +6495,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125703041</v>
+        <v>125703135</v>
       </c>
       <c r="B62" t="n">
         <v>78972</v>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502202</v>
+        <v>502441</v>
       </c>
       <c r="R62" t="n">
-        <v>6762136</v>
+        <v>6761973</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6592,7 +6592,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125703135</v>
+        <v>125703045</v>
       </c>
       <c r="B63" t="n">
         <v>78972</v>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502441</v>
+        <v>502143</v>
       </c>
       <c r="R63" t="n">
-        <v>6761973</v>
+        <v>6762252</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6689,7 +6689,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125703045</v>
+        <v>125703041</v>
       </c>
       <c r="B64" t="n">
         <v>78972</v>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502143</v>
+        <v>502202</v>
       </c>
       <c r="R64" t="n">
-        <v>6762252</v>
+        <v>6762136</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704411</v>
+        <v>125704097</v>
       </c>
       <c r="B71" t="n">
         <v>78972</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502100</v>
+        <v>502069</v>
       </c>
       <c r="R71" t="n">
-        <v>6762414</v>
+        <v>6762427</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704248</v>
+        <v>125704411</v>
       </c>
       <c r="B72" t="n">
         <v>78972</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502091</v>
+        <v>502100</v>
       </c>
       <c r="R72" t="n">
-        <v>6762321</v>
+        <v>6762414</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704224</v>
+        <v>125704248</v>
       </c>
       <c r="B73" t="n">
         <v>78972</v>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502310</v>
+        <v>502091</v>
       </c>
       <c r="R73" t="n">
-        <v>6762110</v>
+        <v>6762321</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704097</v>
+        <v>125704224</v>
       </c>
       <c r="B74" t="n">
         <v>78972</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502069</v>
+        <v>502310</v>
       </c>
       <c r="R74" t="n">
-        <v>6762427</v>
+        <v>6762110</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7853,7 +7853,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125704416</v>
+        <v>125703063</v>
       </c>
       <c r="B76" t="n">
         <v>78972</v>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>502139</v>
+        <v>502048</v>
       </c>
       <c r="R76" t="n">
-        <v>6762359</v>
+        <v>6762403</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7950,7 +7950,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125703063</v>
+        <v>125704416</v>
       </c>
       <c r="B77" t="n">
         <v>78972</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>502048</v>
+        <v>502139</v>
       </c>
       <c r="R77" t="n">
-        <v>6762403</v>
+        <v>6762359</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704102</v>
+        <v>125704414</v>
       </c>
       <c r="B80" t="n">
         <v>78972</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125703071</v>
+        <v>125703061</v>
       </c>
       <c r="B84" t="n">
         <v>78972</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>502078</v>
+        <v>502072</v>
       </c>
       <c r="R84" t="n">
-        <v>6762412</v>
+        <v>6762386</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8726,7 +8726,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125703061</v>
+        <v>125703071</v>
       </c>
       <c r="B85" t="n">
         <v>78972</v>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502072</v>
+        <v>502078</v>
       </c>
       <c r="R85" t="n">
-        <v>6762386</v>
+        <v>6762412</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703038</v>
+        <v>125703052</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502265</v>
+        <v>502090</v>
       </c>
       <c r="R13" t="n">
-        <v>6762114</v>
+        <v>6762313</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703155</v>
+        <v>125703035</v>
       </c>
       <c r="B14" t="n">
         <v>78972</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502545</v>
+        <v>502289</v>
       </c>
       <c r="R14" t="n">
-        <v>6761701</v>
+        <v>6762117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703158</v>
+        <v>125703155</v>
       </c>
       <c r="B15" t="n">
         <v>78972</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502561</v>
+        <v>502545</v>
       </c>
       <c r="R15" t="n">
-        <v>6761653</v>
+        <v>6761701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703140</v>
+        <v>125703158</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502377</v>
+        <v>502561</v>
       </c>
       <c r="R16" t="n">
-        <v>6761992</v>
+        <v>6761653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703052</v>
+        <v>125703140</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502090</v>
+        <v>502377</v>
       </c>
       <c r="R17" t="n">
-        <v>6762313</v>
+        <v>6761992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703035</v>
+        <v>125703038</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502289</v>
+        <v>502265</v>
       </c>
       <c r="R18" t="n">
-        <v>6762117</v>
+        <v>6762114</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125703057</v>
+        <v>125704359</v>
       </c>
       <c r="B82" t="n">
         <v>78972</v>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>502078</v>
+        <v>502583</v>
       </c>
       <c r="R82" t="n">
-        <v>6762346</v>
+        <v>6761383</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8500,12 +8500,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8532,7 +8532,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125704359</v>
+        <v>125703057</v>
       </c>
       <c r="B83" t="n">
         <v>78972</v>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>502583</v>
+        <v>502078</v>
       </c>
       <c r="R83" t="n">
-        <v>6761383</v>
+        <v>6762346</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703109</v>
+        <v>125703116</v>
       </c>
       <c r="B9" t="n">
         <v>78972</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502522</v>
+        <v>502499</v>
       </c>
       <c r="R9" t="n">
-        <v>6761590</v>
+        <v>6761670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703116</v>
+        <v>125703109</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502499</v>
+        <v>502522</v>
       </c>
       <c r="R12" t="n">
-        <v>6761670</v>
+        <v>6761590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703052</v>
+        <v>125703038</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502090</v>
+        <v>502265</v>
       </c>
       <c r="R13" t="n">
-        <v>6762313</v>
+        <v>6762114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703035</v>
+        <v>125703155</v>
       </c>
       <c r="B14" t="n">
         <v>78972</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502289</v>
+        <v>502545</v>
       </c>
       <c r="R14" t="n">
-        <v>6762117</v>
+        <v>6761701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703155</v>
+        <v>125703158</v>
       </c>
       <c r="B15" t="n">
         <v>78972</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502545</v>
+        <v>502561</v>
       </c>
       <c r="R15" t="n">
-        <v>6761701</v>
+        <v>6761653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R16" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703140</v>
+        <v>125703052</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502377</v>
+        <v>502090</v>
       </c>
       <c r="R17" t="n">
-        <v>6761992</v>
+        <v>6762313</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703038</v>
+        <v>125703035</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502265</v>
+        <v>502289</v>
       </c>
       <c r="R18" t="n">
-        <v>6762114</v>
+        <v>6762117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703156</v>
+        <v>125703111</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502540</v>
+        <v>502516</v>
       </c>
       <c r="R22" t="n">
-        <v>6761708</v>
+        <v>6761612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703119</v>
+        <v>125703156</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502363</v>
+        <v>502540</v>
       </c>
       <c r="R23" t="n">
-        <v>6761945</v>
+        <v>6761708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703125</v>
+        <v>125703119</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502314</v>
+        <v>502363</v>
       </c>
       <c r="R24" t="n">
-        <v>6762028</v>
+        <v>6761945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703111</v>
+        <v>125703125</v>
       </c>
       <c r="B25" t="n">
         <v>78972</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502516</v>
+        <v>502314</v>
       </c>
       <c r="R25" t="n">
-        <v>6761612</v>
+        <v>6762028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703118</v>
+        <v>125703152</v>
       </c>
       <c r="B27" t="n">
         <v>78972</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502506</v>
+        <v>502468</v>
       </c>
       <c r="R27" t="n">
-        <v>6761695</v>
+        <v>6761842</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703152</v>
+        <v>125703124</v>
       </c>
       <c r="B28" t="n">
         <v>78972</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502468</v>
+        <v>502334</v>
       </c>
       <c r="R28" t="n">
-        <v>6761842</v>
+        <v>6762017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703124</v>
+        <v>125703133</v>
       </c>
       <c r="B29" t="n">
         <v>78972</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502334</v>
+        <v>502464</v>
       </c>
       <c r="R29" t="n">
-        <v>6762017</v>
+        <v>6761949</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703133</v>
+        <v>125703118</v>
       </c>
       <c r="B30" t="n">
         <v>78972</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502464</v>
+        <v>502506</v>
       </c>
       <c r="R30" t="n">
-        <v>6761949</v>
+        <v>6761695</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -6883,7 +6883,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703129</v>
+        <v>125703127</v>
       </c>
       <c r="B66" t="n">
         <v>78972</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502289</v>
+        <v>502294</v>
       </c>
       <c r="R66" t="n">
-        <v>6762038</v>
+        <v>6762030</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125703154</v>
+        <v>125703129</v>
       </c>
       <c r="B67" t="n">
         <v>78972</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502490</v>
+        <v>502289</v>
       </c>
       <c r="R67" t="n">
-        <v>6761791</v>
+        <v>6762038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125703127</v>
+        <v>125703154</v>
       </c>
       <c r="B68" t="n">
         <v>78972</v>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>502294</v>
+        <v>502490</v>
       </c>
       <c r="R68" t="n">
-        <v>6762030</v>
+        <v>6761791</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704097</v>
+        <v>125704411</v>
       </c>
       <c r="B71" t="n">
         <v>78972</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502069</v>
+        <v>502100</v>
       </c>
       <c r="R71" t="n">
-        <v>6762427</v>
+        <v>6762414</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7465,7 +7465,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704411</v>
+        <v>125704248</v>
       </c>
       <c r="B72" t="n">
         <v>78972</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502100</v>
+        <v>502091</v>
       </c>
       <c r="R72" t="n">
-        <v>6762414</v>
+        <v>6762321</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704248</v>
+        <v>125704224</v>
       </c>
       <c r="B73" t="n">
         <v>78972</v>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502091</v>
+        <v>502310</v>
       </c>
       <c r="R73" t="n">
-        <v>6762321</v>
+        <v>6762110</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704224</v>
+        <v>125704051</v>
       </c>
       <c r="B74" t="n">
         <v>78972</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502310</v>
+        <v>502592</v>
       </c>
       <c r="R74" t="n">
-        <v>6762110</v>
+        <v>6761383</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,7 +7756,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704051</v>
+        <v>125704097</v>
       </c>
       <c r="B75" t="n">
         <v>78972</v>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502592</v>
+        <v>502069</v>
       </c>
       <c r="R75" t="n">
-        <v>6761383</v>
+        <v>6762427</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8920,7 +8920,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125704053</v>
+        <v>125704225</v>
       </c>
       <c r="B87" t="n">
         <v>78972</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>502305</v>
+        <v>502288</v>
       </c>
       <c r="R87" t="n">
-        <v>6762092</v>
+        <v>6762074</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9017,7 +9017,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125704225</v>
+        <v>125703073</v>
       </c>
       <c r="B88" t="n">
         <v>78972</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>502288</v>
+        <v>502087</v>
       </c>
       <c r="R88" t="n">
-        <v>6762074</v>
+        <v>6762398</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9114,7 +9114,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125703073</v>
+        <v>125704053</v>
       </c>
       <c r="B89" t="n">
         <v>78972</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>502087</v>
+        <v>502305</v>
       </c>
       <c r="R89" t="n">
-        <v>6762398</v>
+        <v>6762092</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703036</v>
+        <v>125703142</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502277</v>
+        <v>502396</v>
       </c>
       <c r="R2" t="n">
-        <v>6762122</v>
+        <v>6761943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703142</v>
+        <v>125703036</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502396</v>
+        <v>502277</v>
       </c>
       <c r="R3" t="n">
-        <v>6761943</v>
+        <v>6762122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +872,7 @@
         <v>125703128</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125703141</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125703034</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125703117</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125703137</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125703116</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703134</v>
+        <v>125703109</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502457</v>
+        <v>502522</v>
       </c>
       <c r="R10" t="n">
-        <v>6761959</v>
+        <v>6761590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703121</v>
+        <v>125703134</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502337</v>
+        <v>502457</v>
       </c>
       <c r="R11" t="n">
-        <v>6761987</v>
+        <v>6761959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703109</v>
+        <v>125703121</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502522</v>
+        <v>502337</v>
       </c>
       <c r="R12" t="n">
-        <v>6761590</v>
+        <v>6761987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>125703038</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703155</v>
+        <v>125703052</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502545</v>
+        <v>502090</v>
       </c>
       <c r="R14" t="n">
-        <v>6761701</v>
+        <v>6762313</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703158</v>
+        <v>125703155</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502561</v>
+        <v>502545</v>
       </c>
       <c r="R15" t="n">
-        <v>6761653</v>
+        <v>6761701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703140</v>
+        <v>125703158</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502377</v>
+        <v>502561</v>
       </c>
       <c r="R16" t="n">
-        <v>6761992</v>
+        <v>6761653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703052</v>
+        <v>125703140</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502090</v>
+        <v>502377</v>
       </c>
       <c r="R17" t="n">
-        <v>6762313</v>
+        <v>6761992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2230,7 +2230,7 @@
         <v>125703035</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125703049</v>
+        <v>125703153</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502125</v>
+        <v>502484</v>
       </c>
       <c r="R19" t="n">
-        <v>6762284</v>
+        <v>6761867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2389,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703153</v>
+        <v>125703148</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502484</v>
+        <v>502479</v>
       </c>
       <c r="R20" t="n">
-        <v>6761867</v>
+        <v>6761918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125703148</v>
+        <v>125703049</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>502479</v>
+        <v>502125</v>
       </c>
       <c r="R21" t="n">
-        <v>6761918</v>
+        <v>6762284</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2583,12 +2583,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703111</v>
+        <v>125703156</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502516</v>
+        <v>502540</v>
       </c>
       <c r="R22" t="n">
-        <v>6761612</v>
+        <v>6761708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703156</v>
+        <v>125703119</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502540</v>
+        <v>502363</v>
       </c>
       <c r="R23" t="n">
-        <v>6761708</v>
+        <v>6761945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703119</v>
+        <v>125703111</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502363</v>
+        <v>502516</v>
       </c>
       <c r="R24" t="n">
-        <v>6761945</v>
+        <v>6761612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2909,7 +2909,7 @@
         <v>125703125</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>97223</v>
+        <v>97225</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>125703152</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>125703124</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703133</v>
+        <v>125703118</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502464</v>
+        <v>502506</v>
       </c>
       <c r="R29" t="n">
-        <v>6761949</v>
+        <v>6761695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703118</v>
+        <v>125703133</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502506</v>
+        <v>502464</v>
       </c>
       <c r="R30" t="n">
-        <v>6761695</v>
+        <v>6761949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>125703143</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>125703115</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>125703157</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>125703123</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703113</v>
+        <v>125703126</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502516</v>
+        <v>502300</v>
       </c>
       <c r="R35" t="n">
-        <v>6761621</v>
+        <v>6762030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703136</v>
+        <v>125703113</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502437</v>
+        <v>502516</v>
       </c>
       <c r="R36" t="n">
-        <v>6761976</v>
+        <v>6761621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703033</v>
+        <v>125703136</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502147</v>
+        <v>502437</v>
       </c>
       <c r="R37" t="n">
-        <v>6762242</v>
+        <v>6761976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703110</v>
+        <v>125703033</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502509</v>
+        <v>502147</v>
       </c>
       <c r="R38" t="n">
-        <v>6761598</v>
+        <v>6762242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703147</v>
+        <v>125703131</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502460</v>
+        <v>502297</v>
       </c>
       <c r="R39" t="n">
-        <v>6761921</v>
+        <v>6762055</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703126</v>
+        <v>125703110</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502300</v>
+        <v>502509</v>
       </c>
       <c r="R40" t="n">
-        <v>6762030</v>
+        <v>6761598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703131</v>
+        <v>125703147</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502297</v>
+        <v>502460</v>
       </c>
       <c r="R41" t="n">
-        <v>6762055</v>
+        <v>6761921</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703051</v>
+        <v>125703114</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502107</v>
+        <v>502523</v>
       </c>
       <c r="R42" t="n">
-        <v>6762317</v>
+        <v>6761654</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,10 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703132</v>
+        <v>125703051</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502329</v>
+        <v>502107</v>
       </c>
       <c r="R43" t="n">
-        <v>6762061</v>
+        <v>6762317</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4749,10 +4749,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703139</v>
+        <v>125703042</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502377</v>
+        <v>502201</v>
       </c>
       <c r="R44" t="n">
-        <v>6762023</v>
+        <v>6762164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4846,10 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703114</v>
+        <v>125703139</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502523</v>
+        <v>502377</v>
       </c>
       <c r="R45" t="n">
-        <v>6761654</v>
+        <v>6762023</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703042</v>
+        <v>125703132</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502201</v>
+        <v>502329</v>
       </c>
       <c r="R46" t="n">
-        <v>6762164</v>
+        <v>6762061</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5008,12 +5008,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5043,7 +5043,7 @@
         <v>125703160</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703039</v>
+        <v>125703047</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>502249</v>
+        <v>502134</v>
       </c>
       <c r="R48" t="n">
-        <v>6762132</v>
+        <v>6762272</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125703047</v>
+        <v>125703039</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>502134</v>
+        <v>502249</v>
       </c>
       <c r="R49" t="n">
-        <v>6762272</v>
+        <v>6762132</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703050</v>
+        <v>125703043</v>
       </c>
       <c r="B50" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502130</v>
+        <v>502173</v>
       </c>
       <c r="R50" t="n">
-        <v>6762292</v>
+        <v>6762170</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5431,7 +5431,7 @@
         <v>125703130</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703043</v>
+        <v>125703050</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502173</v>
+        <v>502130</v>
       </c>
       <c r="R52" t="n">
-        <v>6762170</v>
+        <v>6762292</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
         <v>125703122</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>125703149</v>
       </c>
       <c r="B54" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>125703145</v>
       </c>
       <c r="B55" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5913,10 +5913,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703146</v>
+        <v>125703044</v>
       </c>
       <c r="B56" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502447</v>
+        <v>502165</v>
       </c>
       <c r="R56" t="n">
-        <v>6761914</v>
+        <v>6762230</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6010,10 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703112</v>
+        <v>125703146</v>
       </c>
       <c r="B57" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502515</v>
+        <v>502447</v>
       </c>
       <c r="R57" t="n">
-        <v>6761615</v>
+        <v>6761914</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6107,10 +6107,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703037</v>
+        <v>125703112</v>
       </c>
       <c r="B58" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502275</v>
+        <v>502515</v>
       </c>
       <c r="R58" t="n">
-        <v>6762145</v>
+        <v>6761615</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703138</v>
+        <v>125703037</v>
       </c>
       <c r="B59" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502374</v>
+        <v>502275</v>
       </c>
       <c r="R59" t="n">
-        <v>6762057</v>
+        <v>6762145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6301,10 +6301,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703150</v>
+        <v>125703138</v>
       </c>
       <c r="B60" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502446</v>
+        <v>502374</v>
       </c>
       <c r="R60" t="n">
-        <v>6761867</v>
+        <v>6762057</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,10 +6398,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703044</v>
+        <v>125703150</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502165</v>
+        <v>502446</v>
       </c>
       <c r="R61" t="n">
-        <v>6762230</v>
+        <v>6761867</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6495,10 +6495,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125703135</v>
+        <v>125703041</v>
       </c>
       <c r="B62" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>502441</v>
+        <v>502202</v>
       </c>
       <c r="R62" t="n">
-        <v>6761973</v>
+        <v>6762136</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6592,10 +6592,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125703045</v>
+        <v>125703135</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6627,10 +6627,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>502143</v>
+        <v>502441</v>
       </c>
       <c r="R63" t="n">
-        <v>6762252</v>
+        <v>6761973</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6689,10 +6689,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125703041</v>
+        <v>125703045</v>
       </c>
       <c r="B64" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>502202</v>
+        <v>502143</v>
       </c>
       <c r="R64" t="n">
-        <v>6762136</v>
+        <v>6762252</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6789,7 +6789,7 @@
         <v>125703120</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>125703127</v>
       </c>
       <c r="B66" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         <v>125703129</v>
       </c>
       <c r="B67" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         <v>125703154</v>
       </c>
       <c r="B68" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>125704103</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>125703069</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>125704411</v>
       </c>
       <c r="B71" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>125704248</v>
       </c>
       <c r="B72" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>125704224</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>125704051</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>125704097</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>125703063</v>
       </c>
       <c r="B76" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>125704416</v>
       </c>
       <c r="B77" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         <v>125704362</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         <v>125703055</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8241,10 +8241,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704414</v>
+        <v>125704102</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>125703074</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125704359</v>
+        <v>125703057</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>502583</v>
+        <v>502078</v>
       </c>
       <c r="R82" t="n">
-        <v>6761383</v>
+        <v>6762346</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8500,12 +8500,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8532,10 +8532,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125703057</v>
+        <v>125704359</v>
       </c>
       <c r="B83" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>502078</v>
+        <v>502583</v>
       </c>
       <c r="R83" t="n">
-        <v>6762346</v>
+        <v>6761383</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8597,12 +8597,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8629,10 +8629,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125703061</v>
+        <v>125703071</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>502072</v>
+        <v>502078</v>
       </c>
       <c r="R84" t="n">
-        <v>6762386</v>
+        <v>6762412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125703071</v>
+        <v>125703061</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502078</v>
+        <v>502072</v>
       </c>
       <c r="R85" t="n">
-        <v>6762412</v>
+        <v>6762386</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
         <v>125703067</v>
       </c>
       <c r="B86" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>125704225</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>125703073</v>
       </c>
       <c r="B88" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>125704053</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>125703062</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>125703056</v>
       </c>
       <c r="B91" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>125703066</v>
       </c>
       <c r="B92" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>125703064</v>
       </c>
       <c r="B93" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125704222</v>
+        <v>125704055</v>
       </c>
       <c r="B94" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9696,10 +9696,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B95" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R95" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B96" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R96" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9893,7 +9893,7 @@
         <v>125703060</v>
       </c>
       <c r="B97" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>125703058</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -4555,7 +4555,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703114</v>
+        <v>125703051</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502523</v>
+        <v>502107</v>
       </c>
       <c r="R42" t="n">
-        <v>6761654</v>
+        <v>6762317</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,7 +4652,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703051</v>
+        <v>125703042</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502107</v>
+        <v>502201</v>
       </c>
       <c r="R43" t="n">
-        <v>6762317</v>
+        <v>6762164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703042</v>
+        <v>125703139</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4784,10 +4784,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>502201</v>
+        <v>502377</v>
       </c>
       <c r="R44" t="n">
-        <v>6762164</v>
+        <v>6762023</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4846,7 +4846,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703139</v>
+        <v>125703132</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502377</v>
+        <v>502329</v>
       </c>
       <c r="R45" t="n">
-        <v>6762023</v>
+        <v>6762061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703132</v>
+        <v>125703160</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502329</v>
+        <v>502555</v>
       </c>
       <c r="R46" t="n">
-        <v>6762061</v>
+        <v>6761580</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703160</v>
+        <v>125703114</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502555</v>
+        <v>502523</v>
       </c>
       <c r="R47" t="n">
-        <v>6761580</v>
+        <v>6761654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -9696,7 +9696,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B95" t="n">
         <v>78973</v>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R95" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,7 +9793,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B96" t="n">
         <v>78973</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R96" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703142</v>
+        <v>125703141</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502396</v>
+        <v>502408</v>
       </c>
       <c r="R2" t="n">
-        <v>6761943</v>
+        <v>6761981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703036</v>
+        <v>125703034</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502277</v>
+        <v>502119</v>
       </c>
       <c r="R3" t="n">
-        <v>6762122</v>
+        <v>6762355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703128</v>
+        <v>125703142</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502289</v>
+        <v>502396</v>
       </c>
       <c r="R4" t="n">
-        <v>6762035</v>
+        <v>6761943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703141</v>
+        <v>125703036</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502408</v>
+        <v>502277</v>
       </c>
       <c r="R5" t="n">
-        <v>6761981</v>
+        <v>6762122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703034</v>
+        <v>125703128</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502119</v>
+        <v>502289</v>
       </c>
       <c r="R6" t="n">
-        <v>6762355</v>
+        <v>6762035</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703134</v>
+        <v>125703121</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502457</v>
+        <v>502337</v>
       </c>
       <c r="R11" t="n">
-        <v>6761959</v>
+        <v>6761987</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703121</v>
+        <v>125703134</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502337</v>
+        <v>502457</v>
       </c>
       <c r="R12" t="n">
-        <v>6761987</v>
+        <v>6761959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703052</v>
+        <v>125703155</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502090</v>
+        <v>502545</v>
       </c>
       <c r="R14" t="n">
-        <v>6762313</v>
+        <v>6761701</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703155</v>
+        <v>125703158</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502545</v>
+        <v>502561</v>
       </c>
       <c r="R15" t="n">
-        <v>6761701</v>
+        <v>6761653</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R16" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703140</v>
+        <v>125703052</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502377</v>
+        <v>502090</v>
       </c>
       <c r="R17" t="n">
-        <v>6761992</v>
+        <v>6762313</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125703153</v>
+        <v>125703148</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502484</v>
+        <v>502479</v>
       </c>
       <c r="R19" t="n">
-        <v>6761867</v>
+        <v>6761918</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703148</v>
+        <v>125703153</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502479</v>
+        <v>502484</v>
       </c>
       <c r="R20" t="n">
-        <v>6761918</v>
+        <v>6761867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>97225</v>
+        <v>97227</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703124</v>
+        <v>125703133</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502334</v>
+        <v>502464</v>
       </c>
       <c r="R28" t="n">
-        <v>6762017</v>
+        <v>6761949</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703118</v>
+        <v>125703124</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502506</v>
+        <v>502334</v>
       </c>
       <c r="R29" t="n">
-        <v>6761695</v>
+        <v>6762017</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703133</v>
+        <v>125703118</v>
       </c>
       <c r="B30" t="n">
         <v>78973</v>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502464</v>
+        <v>502506</v>
       </c>
       <c r="R30" t="n">
-        <v>6761949</v>
+        <v>6761695</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703113</v>
+        <v>125703033</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502516</v>
+        <v>502147</v>
       </c>
       <c r="R36" t="n">
-        <v>6761621</v>
+        <v>6762242</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703136</v>
+        <v>125703131</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502437</v>
+        <v>502297</v>
       </c>
       <c r="R37" t="n">
-        <v>6761976</v>
+        <v>6762055</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703033</v>
+        <v>125703110</v>
       </c>
       <c r="B38" t="n">
         <v>78973</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502147</v>
+        <v>502509</v>
       </c>
       <c r="R38" t="n">
-        <v>6762242</v>
+        <v>6761598</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703131</v>
+        <v>125703147</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502297</v>
+        <v>502460</v>
       </c>
       <c r="R39" t="n">
-        <v>6762055</v>
+        <v>6761921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703110</v>
+        <v>125703113</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502509</v>
+        <v>502516</v>
       </c>
       <c r="R40" t="n">
-        <v>6761598</v>
+        <v>6761621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703147</v>
+        <v>125703136</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502460</v>
+        <v>502437</v>
       </c>
       <c r="R41" t="n">
-        <v>6761921</v>
+        <v>6761976</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703160</v>
+        <v>125703114</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502555</v>
+        <v>502523</v>
       </c>
       <c r="R46" t="n">
-        <v>6761580</v>
+        <v>6761654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703114</v>
+        <v>125703160</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502523</v>
+        <v>502555</v>
       </c>
       <c r="R47" t="n">
-        <v>6761654</v>
+        <v>6761580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703043</v>
+        <v>125703130</v>
       </c>
       <c r="B50" t="n">
         <v>78973</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502173</v>
+        <v>502291</v>
       </c>
       <c r="R50" t="n">
-        <v>6762170</v>
+        <v>6762055</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125703130</v>
+        <v>125703050</v>
       </c>
       <c r="B51" t="n">
         <v>78973</v>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502291</v>
+        <v>502130</v>
       </c>
       <c r="R51" t="n">
-        <v>6762055</v>
+        <v>6762292</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5525,7 +5525,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703050</v>
+        <v>125703043</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502130</v>
+        <v>502173</v>
       </c>
       <c r="R52" t="n">
-        <v>6762292</v>
+        <v>6762170</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125703044</v>
+        <v>125703146</v>
       </c>
       <c r="B56" t="n">
         <v>78973</v>
@@ -5948,10 +5948,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>502165</v>
+        <v>502447</v>
       </c>
       <c r="R56" t="n">
-        <v>6762230</v>
+        <v>6761914</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703146</v>
+        <v>125703112</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502447</v>
+        <v>502515</v>
       </c>
       <c r="R57" t="n">
-        <v>6761914</v>
+        <v>6761615</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703112</v>
+        <v>125703037</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502515</v>
+        <v>502275</v>
       </c>
       <c r="R58" t="n">
-        <v>6761615</v>
+        <v>6762145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125703037</v>
+        <v>125703138</v>
       </c>
       <c r="B59" t="n">
         <v>78973</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>502275</v>
+        <v>502374</v>
       </c>
       <c r="R59" t="n">
-        <v>6762145</v>
+        <v>6762057</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6269,12 +6269,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703138</v>
+        <v>125703150</v>
       </c>
       <c r="B60" t="n">
         <v>78973</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502374</v>
+        <v>502446</v>
       </c>
       <c r="R60" t="n">
-        <v>6762057</v>
+        <v>6761867</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703150</v>
+        <v>125703044</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502446</v>
+        <v>502165</v>
       </c>
       <c r="R61" t="n">
-        <v>6761867</v>
+        <v>6762230</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6883,7 +6883,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703127</v>
+        <v>125703129</v>
       </c>
       <c r="B66" t="n">
         <v>78973</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502294</v>
+        <v>502289</v>
       </c>
       <c r="R66" t="n">
-        <v>6762030</v>
+        <v>6762038</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125703129</v>
+        <v>125703154</v>
       </c>
       <c r="B67" t="n">
         <v>78973</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502289</v>
+        <v>502490</v>
       </c>
       <c r="R67" t="n">
-        <v>6762038</v>
+        <v>6761791</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7077,7 +7077,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125703154</v>
+        <v>125703127</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>502490</v>
+        <v>502294</v>
       </c>
       <c r="R68" t="n">
-        <v>6761791</v>
+        <v>6762030</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R69" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B70" t="n">
         <v>78973</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R70" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125703141</v>
+        <v>125703142</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502408</v>
+        <v>502396</v>
       </c>
       <c r="R2" t="n">
-        <v>6761981</v>
+        <v>6761943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125703034</v>
+        <v>125703036</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502119</v>
+        <v>502277</v>
       </c>
       <c r="R3" t="n">
-        <v>6762355</v>
+        <v>6762122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125703142</v>
+        <v>125703128</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502396</v>
+        <v>502289</v>
       </c>
       <c r="R4" t="n">
-        <v>6761943</v>
+        <v>6762035</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703036</v>
+        <v>125703117</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502277</v>
+        <v>502502</v>
       </c>
       <c r="R5" t="n">
-        <v>6762122</v>
+        <v>6761684</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703128</v>
+        <v>125703141</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502289</v>
+        <v>502408</v>
       </c>
       <c r="R6" t="n">
-        <v>6762035</v>
+        <v>6761981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703117</v>
+        <v>125703034</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502502</v>
+        <v>502119</v>
       </c>
       <c r="R7" t="n">
-        <v>6761684</v>
+        <v>6762355</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -7174,7 +7174,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R69" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B70" t="n">
         <v>78973</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R70" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703116</v>
+        <v>125703121</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502499</v>
+        <v>502337</v>
       </c>
       <c r="R9" t="n">
-        <v>6761670</v>
+        <v>6761987</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703109</v>
+        <v>125703134</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502522</v>
+        <v>502457</v>
       </c>
       <c r="R10" t="n">
-        <v>6761590</v>
+        <v>6761959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703121</v>
+        <v>125703116</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502337</v>
+        <v>502499</v>
       </c>
       <c r="R11" t="n">
-        <v>6761987</v>
+        <v>6761670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703134</v>
+        <v>125703109</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502457</v>
+        <v>502522</v>
       </c>
       <c r="R12" t="n">
-        <v>6761959</v>
+        <v>6761590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703038</v>
+        <v>125703158</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502265</v>
+        <v>502561</v>
       </c>
       <c r="R13" t="n">
-        <v>6762114</v>
+        <v>6761653</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703155</v>
+        <v>125703035</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502545</v>
+        <v>502289</v>
       </c>
       <c r="R14" t="n">
-        <v>6761701</v>
+        <v>6762117</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R15" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703140</v>
+        <v>125703052</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502377</v>
+        <v>502090</v>
       </c>
       <c r="R16" t="n">
-        <v>6761992</v>
+        <v>6762313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703052</v>
+        <v>125703038</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502090</v>
+        <v>502265</v>
       </c>
       <c r="R17" t="n">
-        <v>6762313</v>
+        <v>6762114</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703035</v>
+        <v>125703155</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502289</v>
+        <v>502545</v>
       </c>
       <c r="R18" t="n">
-        <v>6762117</v>
+        <v>6761701</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125703148</v>
+        <v>125703153</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>502479</v>
+        <v>502484</v>
       </c>
       <c r="R19" t="n">
-        <v>6761918</v>
+        <v>6761867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125703153</v>
+        <v>125703148</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>502484</v>
+        <v>502479</v>
       </c>
       <c r="R20" t="n">
-        <v>6761867</v>
+        <v>6761918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703156</v>
+        <v>125703111</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502540</v>
+        <v>502516</v>
       </c>
       <c r="R22" t="n">
-        <v>6761708</v>
+        <v>6761612</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703119</v>
+        <v>125703125</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502363</v>
+        <v>502314</v>
       </c>
       <c r="R23" t="n">
-        <v>6761945</v>
+        <v>6762028</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703111</v>
+        <v>125703119</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502516</v>
+        <v>502363</v>
       </c>
       <c r="R24" t="n">
-        <v>6761612</v>
+        <v>6761945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703125</v>
+        <v>125703156</v>
       </c>
       <c r="B25" t="n">
         <v>78973</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502314</v>
+        <v>502540</v>
       </c>
       <c r="R25" t="n">
-        <v>6762028</v>
+        <v>6761708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>97227</v>
+        <v>97229</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703152</v>
+        <v>125703124</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502468</v>
+        <v>502334</v>
       </c>
       <c r="R27" t="n">
-        <v>6761842</v>
+        <v>6762017</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703124</v>
+        <v>125703152</v>
       </c>
       <c r="B29" t="n">
         <v>78973</v>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502334</v>
+        <v>502468</v>
       </c>
       <c r="R29" t="n">
-        <v>6762017</v>
+        <v>6761842</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703126</v>
+        <v>125703136</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502300</v>
+        <v>502437</v>
       </c>
       <c r="R35" t="n">
-        <v>6762030</v>
+        <v>6761976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703033</v>
+        <v>125703110</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502147</v>
+        <v>502509</v>
       </c>
       <c r="R36" t="n">
-        <v>6762242</v>
+        <v>6761598</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703131</v>
+        <v>125703147</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502297</v>
+        <v>502460</v>
       </c>
       <c r="R37" t="n">
-        <v>6762055</v>
+        <v>6761921</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703110</v>
+        <v>125703131</v>
       </c>
       <c r="B38" t="n">
         <v>78973</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502509</v>
+        <v>502297</v>
       </c>
       <c r="R38" t="n">
-        <v>6761598</v>
+        <v>6762055</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703147</v>
+        <v>125703033</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502460</v>
+        <v>502147</v>
       </c>
       <c r="R39" t="n">
-        <v>6761921</v>
+        <v>6762242</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703113</v>
+        <v>125703126</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502516</v>
+        <v>502300</v>
       </c>
       <c r="R40" t="n">
-        <v>6761621</v>
+        <v>6762030</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703136</v>
+        <v>125703113</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502437</v>
+        <v>502516</v>
       </c>
       <c r="R41" t="n">
-        <v>6761976</v>
+        <v>6761621</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4555,7 +4555,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703051</v>
+        <v>125703114</v>
       </c>
       <c r="B42" t="n">
         <v>78973</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502107</v>
+        <v>502523</v>
       </c>
       <c r="R42" t="n">
-        <v>6762317</v>
+        <v>6761654</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,7 +4652,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703042</v>
+        <v>125703051</v>
       </c>
       <c r="B43" t="n">
         <v>78973</v>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502201</v>
+        <v>502107</v>
       </c>
       <c r="R43" t="n">
-        <v>6762164</v>
+        <v>6762317</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703132</v>
+        <v>125703160</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502329</v>
+        <v>502555</v>
       </c>
       <c r="R45" t="n">
-        <v>6762061</v>
+        <v>6761580</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703114</v>
+        <v>125703132</v>
       </c>
       <c r="B46" t="n">
         <v>78973</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502523</v>
+        <v>502329</v>
       </c>
       <c r="R46" t="n">
-        <v>6761654</v>
+        <v>6762061</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703160</v>
+        <v>125703042</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502555</v>
+        <v>502201</v>
       </c>
       <c r="R47" t="n">
-        <v>6761580</v>
+        <v>6762164</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5428,7 +5428,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125703050</v>
+        <v>125703043</v>
       </c>
       <c r="B51" t="n">
         <v>78973</v>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502130</v>
+        <v>502173</v>
       </c>
       <c r="R51" t="n">
-        <v>6762292</v>
+        <v>6762170</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5525,7 +5525,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125703043</v>
+        <v>125703050</v>
       </c>
       <c r="B52" t="n">
         <v>78973</v>
@@ -5560,10 +5560,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>502173</v>
+        <v>502130</v>
       </c>
       <c r="R52" t="n">
-        <v>6762170</v>
+        <v>6762292</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703112</v>
+        <v>125703044</v>
       </c>
       <c r="B57" t="n">
         <v>78973</v>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502515</v>
+        <v>502165</v>
       </c>
       <c r="R57" t="n">
-        <v>6761615</v>
+        <v>6762230</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6107,7 +6107,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703037</v>
+        <v>125703112</v>
       </c>
       <c r="B58" t="n">
         <v>78973</v>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502275</v>
+        <v>502515</v>
       </c>
       <c r="R58" t="n">
-        <v>6762145</v>
+        <v>6761615</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6301,7 +6301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703150</v>
+        <v>125703037</v>
       </c>
       <c r="B60" t="n">
         <v>78973</v>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502446</v>
+        <v>502275</v>
       </c>
       <c r="R60" t="n">
-        <v>6761867</v>
+        <v>6762145</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6398,7 +6398,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703044</v>
+        <v>125703150</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502165</v>
+        <v>502446</v>
       </c>
       <c r="R61" t="n">
-        <v>6762230</v>
+        <v>6761867</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6883,7 +6883,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703129</v>
+        <v>125703154</v>
       </c>
       <c r="B66" t="n">
         <v>78973</v>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502289</v>
+        <v>502490</v>
       </c>
       <c r="R66" t="n">
-        <v>6762038</v>
+        <v>6761791</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6980,7 +6980,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125703154</v>
+        <v>125703129</v>
       </c>
       <c r="B67" t="n">
         <v>78973</v>
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>502490</v>
+        <v>502289</v>
       </c>
       <c r="R67" t="n">
-        <v>6761791</v>
+        <v>6762038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7174,7 +7174,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B69" t="n">
         <v>78973</v>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R69" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,7 +7271,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B70" t="n">
         <v>78973</v>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R70" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7368,7 +7368,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704411</v>
+        <v>125704051</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502100</v>
+        <v>502592</v>
       </c>
       <c r="R71" t="n">
-        <v>6762414</v>
+        <v>6761383</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7465,7 +7465,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704248</v>
+        <v>125704097</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502091</v>
+        <v>502069</v>
       </c>
       <c r="R72" t="n">
-        <v>6762321</v>
+        <v>6762427</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704224</v>
+        <v>125704411</v>
       </c>
       <c r="B73" t="n">
         <v>78973</v>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502310</v>
+        <v>502100</v>
       </c>
       <c r="R73" t="n">
-        <v>6762110</v>
+        <v>6762414</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7659,7 +7659,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704051</v>
+        <v>125704248</v>
       </c>
       <c r="B74" t="n">
         <v>78973</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502592</v>
+        <v>502091</v>
       </c>
       <c r="R74" t="n">
-        <v>6761383</v>
+        <v>6762321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,7 +7756,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704097</v>
+        <v>125704224</v>
       </c>
       <c r="B75" t="n">
         <v>78973</v>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502069</v>
+        <v>502310</v>
       </c>
       <c r="R75" t="n">
-        <v>6762427</v>
+        <v>6762110</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8047,7 +8047,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125704362</v>
+        <v>125703055</v>
       </c>
       <c r="B78" t="n">
         <v>78973</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>502594</v>
+        <v>502094</v>
       </c>
       <c r="R78" t="n">
-        <v>6761374</v>
+        <v>6762325</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8144,7 +8144,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125703055</v>
+        <v>125704362</v>
       </c>
       <c r="B79" t="n">
         <v>78973</v>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>502094</v>
+        <v>502594</v>
       </c>
       <c r="R79" t="n">
-        <v>6762325</v>
+        <v>6761374</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8241,7 +8241,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704102</v>
+        <v>125704414</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8629,7 +8629,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125703071</v>
+        <v>125703061</v>
       </c>
       <c r="B84" t="n">
         <v>78973</v>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>502078</v>
+        <v>502072</v>
       </c>
       <c r="R84" t="n">
-        <v>6762412</v>
+        <v>6762386</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8726,7 +8726,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125703061</v>
+        <v>125703071</v>
       </c>
       <c r="B85" t="n">
         <v>78973</v>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502072</v>
+        <v>502078</v>
       </c>
       <c r="R85" t="n">
-        <v>6762386</v>
+        <v>6762412</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125704225</v>
+        <v>125704053</v>
       </c>
       <c r="B87" t="n">
         <v>78973</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>502288</v>
+        <v>502305</v>
       </c>
       <c r="R87" t="n">
-        <v>6762074</v>
+        <v>6762092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9017,7 +9017,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125703073</v>
+        <v>125704225</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>502087</v>
+        <v>502288</v>
       </c>
       <c r="R88" t="n">
-        <v>6762398</v>
+        <v>6762074</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9114,7 +9114,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125704053</v>
+        <v>125703073</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>502305</v>
+        <v>502087</v>
       </c>
       <c r="R89" t="n">
-        <v>6762092</v>
+        <v>6762398</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125704055</v>
+        <v>125704222</v>
       </c>
       <c r="B94" t="n">
         <v>78973</v>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9696,7 +9696,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B95" t="n">
         <v>78973</v>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R95" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,7 +9793,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B96" t="n">
         <v>78973</v>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R96" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703134</v>
+        <v>125703116</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502457</v>
+        <v>502499</v>
       </c>
       <c r="R10" t="n">
-        <v>6761959</v>
+        <v>6761670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703116</v>
+        <v>125703134</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>502499</v>
+        <v>502457</v>
       </c>
       <c r="R11" t="n">
-        <v>6761670</v>
+        <v>6761959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R13" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703035</v>
+        <v>125703052</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>502289</v>
+        <v>502090</v>
       </c>
       <c r="R14" t="n">
-        <v>6762117</v>
+        <v>6762313</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703140</v>
+        <v>125703038</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502377</v>
+        <v>502265</v>
       </c>
       <c r="R15" t="n">
-        <v>6761992</v>
+        <v>6762114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703052</v>
+        <v>125703155</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502090</v>
+        <v>502545</v>
       </c>
       <c r="R16" t="n">
-        <v>6762313</v>
+        <v>6761701</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703038</v>
+        <v>125703158</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502265</v>
+        <v>502561</v>
       </c>
       <c r="R17" t="n">
-        <v>6762114</v>
+        <v>6761653</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125703155</v>
+        <v>125703035</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>502545</v>
+        <v>502289</v>
       </c>
       <c r="R18" t="n">
-        <v>6761701</v>
+        <v>6762117</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2292,12 +2292,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3876,7 +3876,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703136</v>
+        <v>125703033</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502437</v>
+        <v>502147</v>
       </c>
       <c r="R35" t="n">
-        <v>6761976</v>
+        <v>6762242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3973,7 +3973,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703110</v>
+        <v>125703126</v>
       </c>
       <c r="B36" t="n">
         <v>78973</v>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502509</v>
+        <v>502300</v>
       </c>
       <c r="R36" t="n">
-        <v>6761598</v>
+        <v>6762030</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703147</v>
+        <v>125703113</v>
       </c>
       <c r="B37" t="n">
         <v>78973</v>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502460</v>
+        <v>502516</v>
       </c>
       <c r="R37" t="n">
-        <v>6761921</v>
+        <v>6761621</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703131</v>
+        <v>125703136</v>
       </c>
       <c r="B38" t="n">
         <v>78973</v>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502297</v>
+        <v>502437</v>
       </c>
       <c r="R38" t="n">
-        <v>6762055</v>
+        <v>6761976</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703033</v>
+        <v>125703110</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502147</v>
+        <v>502509</v>
       </c>
       <c r="R39" t="n">
-        <v>6762242</v>
+        <v>6761598</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4329,12 +4329,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4361,7 +4361,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703126</v>
+        <v>125703147</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502300</v>
+        <v>502460</v>
       </c>
       <c r="R40" t="n">
-        <v>6762030</v>
+        <v>6761921</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703113</v>
+        <v>125703131</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502516</v>
+        <v>502297</v>
       </c>
       <c r="R41" t="n">
-        <v>6761621</v>
+        <v>6762055</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -8920,7 +8920,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125704053</v>
+        <v>125704225</v>
       </c>
       <c r="B87" t="n">
         <v>78973</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>502305</v>
+        <v>502288</v>
       </c>
       <c r="R87" t="n">
-        <v>6762092</v>
+        <v>6762074</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -8985,12 +8985,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9017,7 +9017,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125704225</v>
+        <v>125703073</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9052,10 +9052,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>502288</v>
+        <v>502087</v>
       </c>
       <c r="R88" t="n">
-        <v>6762074</v>
+        <v>6762398</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9114,7 +9114,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125703073</v>
+        <v>125704053</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9149,10 +9149,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>502087</v>
+        <v>502305</v>
       </c>
       <c r="R89" t="n">
-        <v>6762398</v>
+        <v>6762092</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125703142</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125703036</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125703128</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125703117</v>
+        <v>125703141</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502502</v>
+        <v>502408</v>
       </c>
       <c r="R5" t="n">
-        <v>6761684</v>
+        <v>6761981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125703141</v>
+        <v>125703034</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502408</v>
+        <v>502119</v>
       </c>
       <c r="R6" t="n">
-        <v>6761981</v>
+        <v>6762355</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125703034</v>
+        <v>125703117</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502119</v>
+        <v>502502</v>
       </c>
       <c r="R7" t="n">
-        <v>6762355</v>
+        <v>6761684</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,7 +1260,7 @@
         <v>125703137</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125703121</v>
+        <v>125703116</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502337</v>
+        <v>502499</v>
       </c>
       <c r="R9" t="n">
-        <v>6761987</v>
+        <v>6761670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125703116</v>
+        <v>125703109</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502499</v>
+        <v>502522</v>
       </c>
       <c r="R10" t="n">
-        <v>6761670</v>
+        <v>6761590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>125703134</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703109</v>
+        <v>125703121</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502522</v>
+        <v>502337</v>
       </c>
       <c r="R12" t="n">
-        <v>6761590</v>
+        <v>6761987</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125703140</v>
+        <v>125703038</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>502377</v>
+        <v>502265</v>
       </c>
       <c r="R13" t="n">
-        <v>6761992</v>
+        <v>6762114</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1842,7 +1842,7 @@
         <v>125703052</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125703038</v>
+        <v>125703155</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>502265</v>
+        <v>502545</v>
       </c>
       <c r="R15" t="n">
-        <v>6762114</v>
+        <v>6761701</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703155</v>
+        <v>125703158</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>502545</v>
+        <v>502561</v>
       </c>
       <c r="R16" t="n">
-        <v>6761701</v>
+        <v>6761653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703158</v>
+        <v>125703140</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>502561</v>
+        <v>502377</v>
       </c>
       <c r="R17" t="n">
-        <v>6761653</v>
+        <v>6761992</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2230,7 +2230,7 @@
         <v>125703035</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125703153</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125703148</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>125703049</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125703111</v>
+        <v>125703156</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>502516</v>
+        <v>502540</v>
       </c>
       <c r="R22" t="n">
-        <v>6761612</v>
+        <v>6761708</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125703125</v>
+        <v>125703119</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>502314</v>
+        <v>502363</v>
       </c>
       <c r="R23" t="n">
-        <v>6762028</v>
+        <v>6761945</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125703119</v>
+        <v>125703111</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>502363</v>
+        <v>502516</v>
       </c>
       <c r="R24" t="n">
-        <v>6761945</v>
+        <v>6761612</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125703156</v>
+        <v>125703125</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>502540</v>
+        <v>502314</v>
       </c>
       <c r="R25" t="n">
-        <v>6761708</v>
+        <v>6762028</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3006,7 +3006,7 @@
         <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>97229</v>
+        <v>97233</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703124</v>
+        <v>125703152</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>502334</v>
+        <v>502468</v>
       </c>
       <c r="R27" t="n">
-        <v>6762017</v>
+        <v>6761842</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703133</v>
+        <v>125703124</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>502464</v>
+        <v>502334</v>
       </c>
       <c r="R28" t="n">
-        <v>6761949</v>
+        <v>6762017</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125703152</v>
+        <v>125703118</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>502468</v>
+        <v>502506</v>
       </c>
       <c r="R29" t="n">
-        <v>6761842</v>
+        <v>6761695</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,10 +3391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125703118</v>
+        <v>125703133</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3426,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>502506</v>
+        <v>502464</v>
       </c>
       <c r="R30" t="n">
-        <v>6761695</v>
+        <v>6761949</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3491,7 +3491,7 @@
         <v>125703143</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>125703115</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>125703157</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>125703123</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3876,10 +3876,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125703033</v>
+        <v>125703126</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>502147</v>
+        <v>502300</v>
       </c>
       <c r="R35" t="n">
-        <v>6762242</v>
+        <v>6762030</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3973,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125703126</v>
+        <v>125703113</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>502300</v>
+        <v>502516</v>
       </c>
       <c r="R36" t="n">
-        <v>6762030</v>
+        <v>6761621</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125703113</v>
+        <v>125703136</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4105,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>502516</v>
+        <v>502437</v>
       </c>
       <c r="R37" t="n">
-        <v>6761621</v>
+        <v>6761976</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125703136</v>
+        <v>125703033</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>502437</v>
+        <v>502147</v>
       </c>
       <c r="R38" t="n">
-        <v>6761976</v>
+        <v>6762242</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4232,12 +4232,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4264,10 +4264,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703110</v>
+        <v>125703131</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>502509</v>
+        <v>502297</v>
       </c>
       <c r="R39" t="n">
-        <v>6761598</v>
+        <v>6762055</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4361,10 +4361,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703147</v>
+        <v>125703110</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>502460</v>
+        <v>502509</v>
       </c>
       <c r="R40" t="n">
-        <v>6761921</v>
+        <v>6761598</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703131</v>
+        <v>125703147</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>502297</v>
+        <v>502460</v>
       </c>
       <c r="R41" t="n">
-        <v>6762055</v>
+        <v>6761921</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125703114</v>
+        <v>125703051</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>502523</v>
+        <v>502107</v>
       </c>
       <c r="R42" t="n">
-        <v>6761654</v>
+        <v>6762317</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4652,10 +4652,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703051</v>
+        <v>125703042</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>502107</v>
+        <v>502201</v>
       </c>
       <c r="R43" t="n">
-        <v>6762317</v>
+        <v>6762164</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4752,7 +4752,7 @@
         <v>125703139</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703160</v>
+        <v>125703132</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4881,10 +4881,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>502555</v>
+        <v>502329</v>
       </c>
       <c r="R45" t="n">
-        <v>6761580</v>
+        <v>6762061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125703132</v>
+        <v>125703114</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>502329</v>
+        <v>502523</v>
       </c>
       <c r="R46" t="n">
-        <v>6762061</v>
+        <v>6761654</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5040,10 +5040,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703042</v>
+        <v>125703160</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5075,10 +5075,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>502201</v>
+        <v>502555</v>
       </c>
       <c r="R47" t="n">
-        <v>6762164</v>
+        <v>6761580</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5105,12 +5105,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5140,7 +5140,7 @@
         <v>125703047</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>125703039</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125703130</v>
+        <v>125703043</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>502291</v>
+        <v>502173</v>
       </c>
       <c r="R50" t="n">
-        <v>6762055</v>
+        <v>6762170</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5428,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125703043</v>
+        <v>125703130</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>502173</v>
+        <v>502291</v>
       </c>
       <c r="R51" t="n">
-        <v>6762170</v>
+        <v>6762055</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5528,7 +5528,7 @@
         <v>125703050</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>125703122</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>125703149</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
         <v>125703145</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>125703146</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125703044</v>
+        <v>125703112</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>502165</v>
+        <v>502515</v>
       </c>
       <c r="R57" t="n">
-        <v>6762230</v>
+        <v>6761615</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6107,10 +6107,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125703112</v>
+        <v>125703037</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6142,10 +6142,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>502515</v>
+        <v>502275</v>
       </c>
       <c r="R58" t="n">
-        <v>6761615</v>
+        <v>6762145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6172,12 +6172,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6207,7 +6207,7 @@
         <v>125703138</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125703037</v>
+        <v>125703150</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>502275</v>
+        <v>502446</v>
       </c>
       <c r="R60" t="n">
-        <v>6762145</v>
+        <v>6761867</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6366,12 +6366,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6398,10 +6398,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125703150</v>
+        <v>125703044</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>502446</v>
+        <v>502165</v>
       </c>
       <c r="R61" t="n">
-        <v>6761867</v>
+        <v>6762230</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6463,12 +6463,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6498,7 +6498,7 @@
         <v>125703041</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>125703135</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>125703045</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>125703120</v>
       </c>
       <c r="B65" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6883,10 +6883,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125703154</v>
+        <v>125703127</v>
       </c>
       <c r="B66" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>502490</v>
+        <v>502294</v>
       </c>
       <c r="R66" t="n">
-        <v>6761791</v>
+        <v>6762030</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6983,7 +6983,7 @@
         <v>125703129</v>
       </c>
       <c r="B67" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7077,10 +7077,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125703127</v>
+        <v>125703154</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7112,10 +7112,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>502294</v>
+        <v>502490</v>
       </c>
       <c r="R68" t="n">
-        <v>6762030</v>
+        <v>6761791</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7174,10 +7174,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125703069</v>
+        <v>125704103</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>502052</v>
+        <v>502139</v>
       </c>
       <c r="R69" t="n">
-        <v>6762466</v>
+        <v>6762348</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125704103</v>
+        <v>125703069</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>502139</v>
+        <v>502052</v>
       </c>
       <c r="R70" t="n">
-        <v>6762348</v>
+        <v>6762466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125704051</v>
+        <v>125704411</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7403,10 +7403,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>502592</v>
+        <v>502100</v>
       </c>
       <c r="R71" t="n">
-        <v>6761383</v>
+        <v>6762414</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7465,10 +7465,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125704097</v>
+        <v>125704248</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7500,10 +7500,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>502069</v>
+        <v>502091</v>
       </c>
       <c r="R72" t="n">
-        <v>6762427</v>
+        <v>6762321</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7562,10 +7562,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125704411</v>
+        <v>125704224</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7597,10 +7597,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>502100</v>
+        <v>502310</v>
       </c>
       <c r="R73" t="n">
-        <v>6762414</v>
+        <v>6762110</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7627,12 +7627,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7659,10 +7659,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125704248</v>
+        <v>125704051</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>502091</v>
+        <v>502592</v>
       </c>
       <c r="R74" t="n">
-        <v>6762321</v>
+        <v>6761383</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7724,12 +7724,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7756,10 +7756,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125704224</v>
+        <v>125704097</v>
       </c>
       <c r="B75" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>502310</v>
+        <v>502069</v>
       </c>
       <c r="R75" t="n">
-        <v>6762110</v>
+        <v>6762427</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7856,7 +7856,7 @@
         <v>125703063</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>125704416</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125703055</v>
+        <v>125704362</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>502094</v>
+        <v>502594</v>
       </c>
       <c r="R78" t="n">
-        <v>6762325</v>
+        <v>6761374</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8112,12 +8112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8144,10 +8144,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125704362</v>
+        <v>125703055</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>502594</v>
+        <v>502094</v>
       </c>
       <c r="R79" t="n">
-        <v>6761374</v>
+        <v>6762325</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8209,12 +8209,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8241,10 +8241,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125704414</v>
+        <v>125704102</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>125703074</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8438,7 +8438,7 @@
         <v>125703057</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>125704359</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125703061</v>
+        <v>125703071</v>
       </c>
       <c r="B84" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>502072</v>
+        <v>502078</v>
       </c>
       <c r="R84" t="n">
-        <v>6762386</v>
+        <v>6762412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125703071</v>
+        <v>125703061</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8761,10 +8761,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>502078</v>
+        <v>502072</v>
       </c>
       <c r="R85" t="n">
-        <v>6762412</v>
+        <v>6762386</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
         <v>125703067</v>
       </c>
       <c r="B86" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>125704225</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>125703073</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>125704053</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>125703062</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>125703056</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>125703066</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>125703064</v>
       </c>
       <c r="B93" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9599,10 +9599,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125704222</v>
+        <v>125704055</v>
       </c>
       <c r="B94" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9664,12 +9664,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9696,10 +9696,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125703059</v>
+        <v>125703068</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9731,10 +9731,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>502082</v>
+        <v>502041</v>
       </c>
       <c r="R95" t="n">
-        <v>6762356</v>
+        <v>6762433</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9793,10 +9793,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125703068</v>
+        <v>125703059</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>502041</v>
+        <v>502082</v>
       </c>
       <c r="R96" t="n">
-        <v>6762433</v>
+        <v>6762356</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9893,7 +9893,7 @@
         <v>125703060</v>
       </c>
       <c r="B97" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>125703058</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 10374-2025 artfynd.xlsx
+++ b/artfynd/A 10374-2025 artfynd.xlsx
@@ -3006,7 +3006,7 @@
         <v>125703032</v>
       </c>
       <c r="B26" t="n">
-        <v>97233</v>
+        <v>97236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
